--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ22"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0201</v>
+        <v>0.0572</v>
       </c>
       <c r="E2">
-        <v>-0.14</v>
+        <v>-0.174</v>
       </c>
       <c r="G2">
-        <v>0.06139902471834538</v>
+        <v>-0.01480988360933219</v>
       </c>
       <c r="H2">
-        <v>0.06139902471834538</v>
+        <v>-0.01480988360933219</v>
       </c>
       <c r="I2">
-        <v>0.01815416142804546</v>
+        <v>-0.01886348962604917</v>
       </c>
       <c r="J2">
-        <v>0.01512370766838077</v>
+        <v>-0.01595400023251066</v>
       </c>
       <c r="K2">
-        <v>27.012</v>
+        <v>-135.393</v>
       </c>
       <c r="L2">
-        <v>0.005046802309287597</v>
+        <v>-0.02362590957474654</v>
       </c>
       <c r="M2">
-        <v>26</v>
+        <v>0.028</v>
       </c>
       <c r="N2">
-        <v>0.003305701062910034</v>
+        <v>4.809922182330407e-06</v>
       </c>
       <c r="O2">
-        <v>0.962535169554272</v>
+        <v>-0.0002068053739853611</v>
       </c>
       <c r="P2">
-        <v>26</v>
+        <v>0.028</v>
       </c>
       <c r="Q2">
-        <v>0.003305701062910034</v>
+        <v>4.809922182330407e-06</v>
       </c>
       <c r="R2">
-        <v>0.962535169554272</v>
+        <v>-0.0002068053739853611</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1107.94</v>
+        <v>1412.63</v>
       </c>
       <c r="V2">
-        <v>0.1408660936784824</v>
+        <v>0.2426657275866215</v>
       </c>
       <c r="W2">
-        <v>-0.02331802721088436</v>
+        <v>-0.1339092872570194</v>
       </c>
       <c r="X2">
-        <v>0.04891087098572365</v>
+        <v>0.0825976341140761</v>
       </c>
       <c r="Y2">
-        <v>-0.07222889819660801</v>
+        <v>-0.2165069213710956</v>
       </c>
       <c r="Z2">
-        <v>3.824643879151191</v>
+        <v>3.734892802769609</v>
       </c>
       <c r="AA2">
-        <v>0.01757277111617191</v>
+        <v>-0.2192038730500269</v>
       </c>
       <c r="AB2">
-        <v>0.04882001818790439</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC2">
-        <v>-0.03124375901309373</v>
+        <v>-0.3016464302485284</v>
       </c>
       <c r="AD2">
-        <v>36.907</v>
+        <v>27.118</v>
       </c>
       <c r="AE2">
-        <v>0.01740894336146717</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>36.92440894336146</v>
+        <v>27.118</v>
       </c>
       <c r="AG2">
-        <v>-1071.015591056639</v>
+        <v>-1385.512</v>
       </c>
       <c r="AH2">
-        <v>0.004672719262882225</v>
+        <v>0.004636809475656494</v>
       </c>
       <c r="AI2">
-        <v>0.01170340421859681</v>
+        <v>0.009479802895048886</v>
       </c>
       <c r="AJ2">
-        <v>-0.1576371094147567</v>
+        <v>-0.31234856129283</v>
       </c>
       <c r="AK2">
-        <v>-0.5231932881274525</v>
+        <v>-0.9568598417931765</v>
       </c>
       <c r="AL2">
-        <v>0.309</v>
+        <v>0.27</v>
       </c>
       <c r="AM2">
-        <v>0.309</v>
+        <v>0.27</v>
       </c>
       <c r="AN2">
-        <v>0.3127685358598656</v>
+        <v>-0.3381718418755456</v>
       </c>
       <c r="AO2">
-        <v>314.4077669902913</v>
+        <v>-400.374074074074</v>
       </c>
       <c r="AP2">
-        <v>-9.076326396019006</v>
+        <v>17.27786507045766</v>
       </c>
       <c r="AQ2">
-        <v>314.4077669902913</v>
+        <v>-400.374074074074</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Gulf General Cooperative Insurance Company (SASE:8260)</t>
+          <t>Al-Etihad Cooperative Insurance Company (SASE:8170)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,25 +722,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0548</v>
+        <v>0.0524</v>
+      </c>
+      <c r="E3">
+        <v>-0.201</v>
       </c>
       <c r="G3">
-        <v>0.04417910447761194</v>
+        <v>0.0520951302378256</v>
       </c>
       <c r="H3">
-        <v>0.04417910447761194</v>
+        <v>0.0520951302378256</v>
       </c>
       <c r="I3">
-        <v>-0.2522388059701492</v>
+        <v>0.03669309173272934</v>
       </c>
       <c r="J3">
-        <v>-0.2522388059701492</v>
+        <v>0.01993110705981761</v>
       </c>
       <c r="K3">
-        <v>-17.9</v>
+        <v>5.22</v>
       </c>
       <c r="L3">
-        <v>-0.2671641791044776</v>
+        <v>0.01970554926387316</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +752,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,73 +761,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="V3">
-        <v>0.47534165181224</v>
+        <v>0.4527885146327996</v>
       </c>
       <c r="W3">
-        <v>-0.3925438596491228</v>
+        <v>0.03473053892215568</v>
       </c>
       <c r="X3">
-        <v>0.04888835977486764</v>
+        <v>0.0827760817659379</v>
       </c>
       <c r="Y3">
-        <v>-0.4414322194239904</v>
+        <v>-0.04804554284378221</v>
       </c>
       <c r="Z3">
-        <v>-7.477678571428572</v>
+        <v>9.383966842608658</v>
       </c>
       <c r="AA3">
-        <v>1.886160714285714</v>
+        <v>0.1870328477858118</v>
       </c>
       <c r="AB3">
-        <v>0.04882810914982665</v>
+        <v>0.08241619739254631</v>
       </c>
       <c r="AC3">
-        <v>1.837332605135888</v>
+        <v>0.1046166503932654</v>
       </c>
       <c r="AD3">
-        <v>0.468</v>
+        <v>1.73</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.468</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>-79.532</v>
+        <v>-80.27</v>
       </c>
       <c r="AH3">
-        <v>0.002773037542662116</v>
+        <v>0.009462342066400483</v>
       </c>
       <c r="AI3">
-        <v>0.004371053909664887</v>
+        <v>0.01146226727622077</v>
       </c>
       <c r="AJ3">
-        <v>-0.8959534967555874</v>
+        <v>-0.7960924328076961</v>
       </c>
       <c r="AK3">
-        <v>-2.938229643859909</v>
+        <v>-1.164514725083418</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.116</v>
       </c>
       <c r="AN3">
-        <v>-0.02906832298136646</v>
+        <v>0.1632075471698113</v>
+      </c>
+      <c r="AO3">
+        <v>83.79310344827586</v>
       </c>
       <c r="AP3">
-        <v>4.939875776397515</v>
+        <v>-7.572641509433963</v>
+      </c>
+      <c r="AQ3">
+        <v>83.79310344827586</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wataniya Insurance Company (SASE:8300)</t>
+          <t>Alinma Tokio Marine Company (SASE:8312)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,25 +853,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09970000000000001</v>
+        <v>0.0572</v>
       </c>
       <c r="G4">
-        <v>0.03438155136268344</v>
+        <v>-0.03350427350427351</v>
       </c>
       <c r="H4">
-        <v>0.03438155136268344</v>
+        <v>-0.03350427350427351</v>
       </c>
       <c r="I4">
-        <v>-0.07127882599580712</v>
+        <v>0.009709401709401709</v>
       </c>
       <c r="J4">
-        <v>-0.07127882599580712</v>
+        <v>0.004854700854700854</v>
       </c>
       <c r="K4">
-        <v>-11.4</v>
+        <v>-0.139</v>
       </c>
       <c r="L4">
-        <v>-0.07966457023060797</v>
+        <v>-0.002376068376068376</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,55 +895,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>32.7</v>
+        <v>36</v>
       </c>
       <c r="V4">
-        <v>0.150483202945237</v>
+        <v>0.3757828810020877</v>
       </c>
       <c r="W4">
-        <v>-0.1688888888888889</v>
+        <v>-0.00271484375</v>
       </c>
       <c r="X4">
-        <v>0.04881336106789308</v>
+        <v>0.0826903813228855</v>
       </c>
       <c r="Y4">
-        <v>-0.217702249956782</v>
+        <v>-0.0854052250728855</v>
       </c>
       <c r="Z4">
-        <v>-7.735135135135135</v>
+        <v>33.62068965517238</v>
       </c>
       <c r="AA4">
-        <v>0.5513513513513513</v>
+        <v>0.1632183908045975</v>
       </c>
       <c r="AB4">
-        <v>0.04881336106789308</v>
+        <v>0.08246633916140199</v>
       </c>
       <c r="AC4">
-        <v>0.5025379902834581</v>
+        <v>0.0807520516431955</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="AG4">
-        <v>-32.7</v>
+        <v>-35.32</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.007048092868988391</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.01313248358439552</v>
       </c>
       <c r="AJ4">
-        <v>-0.1771397616468039</v>
+        <v>-0.5839947089947091</v>
       </c>
       <c r="AK4">
-        <v>-1.391489361702128</v>
+        <v>-2.238276299112801</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -943,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>-0</v>
+        <v>0.422360248447205</v>
       </c>
       <c r="AP4">
-        <v>3.601321585903084</v>
+        <v>-21.93788819875776</v>
       </c>
     </row>
     <row r="5">
@@ -957,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Rajhi Company for Cooperative Insurance (SASE:8230)</t>
+          <t>The Company for Cooperative Insurance (SASE:8010)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -966,100 +975,103 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.11</v>
+        <v>0.0555</v>
       </c>
       <c r="E5">
-        <v>0.217</v>
+        <v>-0.147</v>
       </c>
       <c r="G5">
-        <v>0.1086302454473476</v>
+        <v>0.03754792152146133</v>
       </c>
       <c r="H5">
-        <v>0.1086302454473476</v>
+        <v>0.03754792152146133</v>
       </c>
       <c r="I5">
-        <v>0.0894695170229612</v>
+        <v>0.03976546643614223</v>
       </c>
       <c r="J5">
-        <v>0.07600950118764846</v>
+        <v>0.03170139975420827</v>
       </c>
       <c r="K5">
-        <v>48</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L5">
-        <v>0.07600950118764846</v>
+        <v>0.03217319401638728</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.028</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>1.045634476062439e-05</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.0003271028037383178</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.028</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>1.045634476062439e-05</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.0003271028037383178</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>105.4</v>
+        <v>371.9</v>
       </c>
       <c r="V5">
-        <v>0.1273254409277604</v>
+        <v>0.1388826648741504</v>
       </c>
       <c r="W5">
-        <v>0.1693719124911786</v>
+        <v>0.1062562065541211</v>
       </c>
       <c r="X5">
-        <v>0.04928904608513515</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y5">
-        <v>0.1200828664060434</v>
+        <v>0.02381364935561962</v>
       </c>
       <c r="Z5">
-        <v>6.119186046511628</v>
+        <v>4.141011673151751</v>
       </c>
       <c r="AA5">
-        <v>0.4651162790697675</v>
+        <v>0.1312758664374265</v>
       </c>
       <c r="AB5">
-        <v>0.04884150951348354</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC5">
-        <v>0.416274769556284</v>
+        <v>0.04883330923892495</v>
       </c>
       <c r="AD5">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-90.80000000000001</v>
+        <v>-371.9</v>
       </c>
       <c r="AH5">
-        <v>0.01733143399810066</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.04006586169045005</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.123202170963365</v>
+        <v>-0.1612819289648293</v>
       </c>
       <c r="AK5">
-        <v>-0.3505791505791506</v>
+        <v>-0.7625589501742873</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1068,10 +1080,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0.2474576271186441</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-1.538983050847458</v>
+        <v>-3.214347450302506</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AXA Cooperative Insurance Company (SASE:8250)</t>
+          <t>Aljazira Takaful Taawuni Company (SASE:8012)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,28 +1103,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0487</v>
+        <v>0.29</v>
       </c>
       <c r="E6">
-        <v>0.299</v>
+        <v>-0.0326</v>
       </c>
       <c r="G6">
-        <v>0.1275130817956486</v>
+        <v>0.168</v>
       </c>
       <c r="H6">
-        <v>0.1275130817956486</v>
+        <v>0.168</v>
       </c>
       <c r="I6">
-        <v>0.1217295510878546</v>
+        <v>0.1691764705882353</v>
       </c>
       <c r="J6">
-        <v>0.1028891364763025</v>
+        <v>0.1620235294117647</v>
       </c>
       <c r="K6">
-        <v>37.2</v>
+        <v>6.88</v>
       </c>
       <c r="L6">
-        <v>0.1024511153952079</v>
+        <v>0.1618823529411765</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1136,73 +1148,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>40.1</v>
+        <v>30.6</v>
       </c>
       <c r="V6">
-        <v>0.09124004550625711</v>
+        <v>0.1421933085501859</v>
       </c>
       <c r="W6">
-        <v>0.1685545990031717</v>
+        <v>0.03182238667900093</v>
       </c>
       <c r="X6">
-        <v>0.04912817252141442</v>
+        <v>0.08257137575023242</v>
       </c>
       <c r="Y6">
-        <v>0.1194264264817573</v>
+        <v>-0.05074898907123149</v>
       </c>
       <c r="Z6">
-        <v>4.213763490774052</v>
+        <v>0.3600474415452389</v>
       </c>
       <c r="AA6">
-        <v>0.4335504868811124</v>
+        <v>0.05833615723483565</v>
       </c>
       <c r="AB6">
-        <v>0.04883209972752673</v>
+        <v>0.08243231666977378</v>
       </c>
       <c r="AC6">
-        <v>0.3847183871535857</v>
+        <v>-0.02409615943493813</v>
       </c>
       <c r="AD6">
-        <v>5.13</v>
+        <v>0.794</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>5.13</v>
+        <v>0.794</v>
       </c>
       <c r="AG6">
-        <v>-34.97</v>
+        <v>-29.806</v>
       </c>
       <c r="AH6">
-        <v>0.01153768301734026</v>
+        <v>0.003676028037815865</v>
       </c>
       <c r="AI6">
-        <v>0.01930530990102736</v>
+        <v>0.003544737805476933</v>
       </c>
       <c r="AJ6">
-        <v>-0.08644599906063827</v>
+        <v>-0.1607711144912996</v>
       </c>
       <c r="AK6">
-        <v>-0.15498825510792</v>
+        <v>-0.1541206035347529</v>
       </c>
       <c r="AL6">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.205</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.1112798264642082</v>
-      </c>
-      <c r="AO6">
-        <v>215.609756097561</v>
+        <v>0.09418742586002374</v>
       </c>
       <c r="AP6">
-        <v>-0.7585683297180043</v>
-      </c>
-      <c r="AQ6">
-        <v>215.609756097561</v>
+        <v>-3.53570581257414</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1219,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Allied Cooperative Insurance Group (SASE:8150)</t>
+          <t>Al Rajhi Company for Cooperative Insurance (SASE:8230)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1222,25 +1228,28 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0123</v>
+        <v>-0.00681</v>
+      </c>
+      <c r="E7">
+        <v>-0.221</v>
       </c>
       <c r="G7">
-        <v>0.01082118188795088</v>
+        <v>0.05063098677208453</v>
       </c>
       <c r="H7">
-        <v>0.01082118188795088</v>
+        <v>0.05063098677208453</v>
       </c>
       <c r="I7">
-        <v>-0.06838066001534919</v>
+        <v>0.01885358065987532</v>
       </c>
       <c r="J7">
-        <v>-0.06838066001534919</v>
+        <v>0.01885358065987532</v>
       </c>
       <c r="K7">
-        <v>-10.5</v>
+        <v>13</v>
       </c>
       <c r="L7">
-        <v>-0.08058326937835764</v>
+        <v>0.01976585069180477</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1249,7 +1258,7 @@
         <v>-0</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7">
         <v>-0</v>
@@ -1258,61 +1267,61 @@
         <v>-0</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="U7">
-        <v>60.2</v>
+        <v>198.3</v>
       </c>
       <c r="V7">
-        <v>0.3291416074357573</v>
+        <v>0.2081452713341031</v>
       </c>
       <c r="W7">
-        <v>-0.2592592592592592</v>
+        <v>0.03716409376786735</v>
       </c>
       <c r="X7">
-        <v>0.04892970810729196</v>
+        <v>0.08287866210511402</v>
       </c>
       <c r="Y7">
-        <v>-0.3081889673665512</v>
+        <v>-0.04571456833724667</v>
       </c>
       <c r="Z7">
-        <v>-3.739954075774971</v>
+        <v>2.53938223938224</v>
       </c>
       <c r="AA7">
-        <v>0.2557405281285878</v>
+        <v>0.04787644787644788</v>
       </c>
       <c r="AB7">
-        <v>0.04882033718517056</v>
+        <v>0.08240819006825183</v>
       </c>
       <c r="AC7">
-        <v>0.2069201909434173</v>
+        <v>-0.03453174219180395</v>
       </c>
       <c r="AD7">
-        <v>0.789</v>
+        <v>11.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.789</v>
+        <v>11.9</v>
       </c>
       <c r="AG7">
-        <v>-59.411</v>
+        <v>-186.4</v>
       </c>
       <c r="AH7">
-        <v>0.004295303474895067</v>
+        <v>0.0123367198838897</v>
       </c>
       <c r="AI7">
-        <v>0.02562603527233752</v>
+        <v>0.03277334067749932</v>
       </c>
       <c r="AJ7">
-        <v>-0.4811035800759582</v>
+        <v>-0.2432467701944408</v>
       </c>
       <c r="AK7">
-        <v>2.020026520689538</v>
+        <v>-1.131067961165049</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1321,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>-0.09238875878220142</v>
+        <v>0.7041420118343196</v>
       </c>
       <c r="AP7">
-        <v>6.956791569086652</v>
+        <v>-11.02958579881657</v>
       </c>
     </row>
     <row r="8">
@@ -1335,7 +1344,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Company for Cooperative Insurance (SASE:8010)</t>
+          <t>Chubb Arabia Cooperative Insurance Company (SASE:8240)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1344,79 +1353,76 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0279</v>
+        <v>-0.006770000000000001</v>
       </c>
       <c r="E8">
-        <v>-0.144</v>
+        <v>-0.449</v>
       </c>
       <c r="G8">
-        <v>0.06753355704697987</v>
+        <v>0.1065902578796562</v>
       </c>
       <c r="H8">
-        <v>0.06753355704697987</v>
+        <v>0.1065902578796562</v>
       </c>
       <c r="I8">
-        <v>0.05494966442953021</v>
+        <v>0.06361031518624642</v>
       </c>
       <c r="J8">
-        <v>0.0386372110365399</v>
+        <v>0.03180515759312321</v>
       </c>
       <c r="K8">
-        <v>82.90000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="L8">
-        <v>0.0386372110365399</v>
+        <v>0.01575931232091691</v>
       </c>
       <c r="M8">
-        <v>26</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.01007634771150641</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.3136308805790108</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>26</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.01007634771150641</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3136308805790108</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>163.1</v>
+        <v>43.4</v>
       </c>
       <c r="V8">
-        <v>0.06320970429794985</v>
+        <v>0.3508488278092158</v>
       </c>
       <c r="W8">
-        <v>0.1150110987791343</v>
+        <v>0.005729166666666667</v>
       </c>
       <c r="X8">
-        <v>0.04881336106789308</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y8">
-        <v>0.06619773771124123</v>
+        <v>-0.07671339053183485</v>
       </c>
       <c r="Z8">
-        <v>3.1373007749671</v>
+        <v>0.527190332326284</v>
       </c>
       <c r="AA8">
-        <v>0.121216552127504</v>
+        <v>0.01676737160120846</v>
       </c>
       <c r="AB8">
-        <v>0.04881336106789308</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC8">
-        <v>0.07240319105961096</v>
+        <v>-0.06567518559729306</v>
       </c>
       <c r="AD8">
         <v>0</v>
@@ -1428,7 +1434,7 @@
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>-163.1</v>
+        <v>-43.4</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1437,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.06747476418997186</v>
+        <v>-0.5404732254047322</v>
       </c>
       <c r="AK8">
-        <v>-0.253852140077821</v>
+        <v>-0.8314176245210728</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1452,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>-1.324939073923639</v>
+        <v>-18.15899581589958</v>
       </c>
     </row>
     <row r="9">
@@ -1463,7 +1469,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chubb Arabia Cooperative Insurance Company (SASE:8240)</t>
+          <t>Arabia Insurance Cooperative Company (SASE:8160)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1472,28 +1478,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.00344</v>
-      </c>
-      <c r="E9">
-        <v>-0.14</v>
+        <v>0.0712</v>
       </c>
       <c r="G9">
-        <v>0.2911504424778761</v>
+        <v>0.007662100456621004</v>
       </c>
       <c r="H9">
-        <v>0.2911504424778761</v>
+        <v>0.007662100456621004</v>
       </c>
       <c r="I9">
-        <v>0.1404129793510324</v>
+        <v>0.001378995433789954</v>
       </c>
       <c r="J9">
-        <v>0.1145132743362832</v>
+        <v>0.0006894977168949772</v>
       </c>
       <c r="K9">
-        <v>3.88</v>
+        <v>-0.914</v>
       </c>
       <c r="L9">
-        <v>0.1144542772861357</v>
+        <v>-0.00834703196347032</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1502,7 +1505,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1511,61 +1514,61 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>29.8</v>
+        <v>50.8</v>
       </c>
       <c r="V9">
-        <v>0.1020198562136255</v>
+        <v>0.3602836879432624</v>
       </c>
       <c r="W9">
-        <v>0.04226579520697168</v>
+        <v>-0.01538720538720539</v>
       </c>
       <c r="X9">
-        <v>0.04881336106789308</v>
+        <v>0.08252674709607594</v>
       </c>
       <c r="Y9">
-        <v>-0.006547565860921402</v>
+        <v>-0.09791395248328133</v>
       </c>
       <c r="Z9">
-        <v>0.7182964297065367</v>
+        <v>3.587223587223588</v>
       </c>
       <c r="AA9">
-        <v>0.08225447610975739</v>
+        <v>0.002473382473382474</v>
       </c>
       <c r="AB9">
-        <v>0.04881336106789308</v>
+        <v>0.08245798695575578</v>
       </c>
       <c r="AC9">
-        <v>0.03344111504186431</v>
+        <v>-0.07998460448237331</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="AG9">
-        <v>-29.8</v>
+        <v>-50.45999999999999</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.002405546908164709</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.005817932922655715</v>
       </c>
       <c r="AJ9">
-        <v>-0.1136103698055661</v>
+        <v>-0.5573227302849568</v>
       </c>
       <c r="AK9">
-        <v>-0.4501510574018127</v>
+        <v>-6.60471204188481</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1574,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>0.3732162458836444</v>
       </c>
       <c r="AP9">
-        <v>-6.234309623430963</v>
+        <v>-55.38968166849615</v>
       </c>
     </row>
     <row r="10">
@@ -1588,7 +1591,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Aljazira Takaful Taawuni Company (SASE:8012)</t>
+          <t>Allianz Saudi Fransi Cooperative Insurance Company (SASE:8040)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1597,28 +1600,28 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.37</v>
+        <v>-0.0519</v>
       </c>
       <c r="E10">
-        <v>0.00553</v>
+        <v>-0.105</v>
       </c>
       <c r="G10">
-        <v>0.2118811881188119</v>
+        <v>-0.06643783371472159</v>
       </c>
       <c r="H10">
-        <v>0.2118811881188119</v>
+        <v>-0.06643783371472159</v>
       </c>
       <c r="I10">
-        <v>0.1354455445544555</v>
+        <v>-0.008924485125858124</v>
       </c>
       <c r="J10">
-        <v>0.1283960396039604</v>
+        <v>-0.005174605679616332</v>
       </c>
       <c r="K10">
-        <v>6.49</v>
+        <v>4.54</v>
       </c>
       <c r="L10">
-        <v>0.1285148514851485</v>
+        <v>0.03463005339435546</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1642,55 +1645,55 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>37.4</v>
+        <v>54.5</v>
       </c>
       <c r="V10">
-        <v>0.1273841961852861</v>
+        <v>0.2605162523900574</v>
       </c>
       <c r="W10">
-        <v>0.05192</v>
+        <v>0.02399577167019028</v>
       </c>
       <c r="X10">
-        <v>0.04893645617369955</v>
+        <v>0.08270791729771995</v>
       </c>
       <c r="Y10">
-        <v>0.00298354382630045</v>
+        <v>-0.05871214562752967</v>
       </c>
       <c r="Z10">
-        <v>0.4372672958697723</v>
+        <v>0.9045371750289783</v>
       </c>
       <c r="AA10">
-        <v>0.05614338903801195</v>
+        <v>-0.004680623203329064</v>
       </c>
       <c r="AB10">
-        <v>0.04882073995799417</v>
+        <v>0.08242154407149202</v>
       </c>
       <c r="AC10">
-        <v>0.007322649080017785</v>
+        <v>-0.08710216727482109</v>
       </c>
       <c r="AD10">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.34</v>
+        <v>1.59</v>
       </c>
       <c r="AG10">
-        <v>-36.06</v>
+        <v>-52.91</v>
       </c>
       <c r="AH10">
-        <v>0.004543296941750865</v>
+        <v>0.007543052326960483</v>
       </c>
       <c r="AI10">
-        <v>0.00615978670589317</v>
+        <v>0.008679513073857744</v>
       </c>
       <c r="AJ10">
-        <v>-0.1400170847247029</v>
+        <v>-0.3385373344423828</v>
       </c>
       <c r="AK10">
-        <v>-0.2001776396136338</v>
+        <v>-0.4111430569585826</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1699,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="AN10">
-        <v>0.1711366538952746</v>
+        <v>-11.27659574468085</v>
       </c>
       <c r="AP10">
-        <v>-4.605363984674329</v>
+        <v>375.2482269503546</v>
       </c>
     </row>
     <row r="11">
@@ -1713,7 +1716,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arabia Insurance Cooperative Company (SASE:8160)</t>
+          <t>Saudi Arabian Cooperative Insurance Company (SASE:8100)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1722,28 +1725,25 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.04219999999999999</v>
-      </c>
-      <c r="E11">
-        <v>-0.278</v>
+        <v>0.0167</v>
       </c>
       <c r="G11">
-        <v>0.04955070603337612</v>
+        <v>-0.0799543118218161</v>
       </c>
       <c r="H11">
-        <v>0.04955070603337612</v>
+        <v>-0.0799543118218161</v>
       </c>
       <c r="I11">
-        <v>0.02747111681643132</v>
+        <v>-0.0930896630496859</v>
       </c>
       <c r="J11">
-        <v>0.01373555840821566</v>
+        <v>-0.0930896630496859</v>
       </c>
       <c r="K11">
-        <v>0.532</v>
+        <v>-18.8</v>
       </c>
       <c r="L11">
-        <v>0.006829268292682927</v>
+        <v>-0.1073672187321531</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1752,7 +1752,7 @@
         <v>-0</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1761,61 +1761,61 @@
         <v>-0</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>29.8</v>
+        <v>2.45</v>
       </c>
       <c r="V11">
-        <v>0.1067335243553009</v>
+        <v>0.02573529411764706</v>
       </c>
       <c r="W11">
-        <v>0.009016949152542373</v>
+        <v>-0.2243436754176611</v>
       </c>
       <c r="X11">
-        <v>0.04890271596470627</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y11">
-        <v>-0.03988576681216389</v>
+        <v>-0.3067862326161627</v>
       </c>
       <c r="Z11">
-        <v>2.673301304049416</v>
+        <v>2.354760623991393</v>
       </c>
       <c r="AA11">
-        <v>0.03671928620452986</v>
+        <v>-0.2192038730500269</v>
       </c>
       <c r="AB11">
-        <v>0.04881872409241687</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC11">
-        <v>-0.01209943788788702</v>
+        <v>-0.3016464302485284</v>
       </c>
       <c r="AD11">
-        <v>0.925</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.925</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>-28.875</v>
+        <v>-2.45</v>
       </c>
       <c r="AH11">
-        <v>0.003302097278000893</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.01533360961458765</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-0.115350044941576</v>
+        <v>-0.02641509433962264</v>
       </c>
       <c r="AK11">
-        <v>-0.9459459459459459</v>
+        <v>-0.03942075623491553</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>0.3303571428571429</v>
+        <v>-0</v>
       </c>
       <c r="AP11">
-        <v>-10.3125</v>
+        <v>0.1560509554140128</v>
       </c>
     </row>
     <row r="12">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AlAhli Takaful Company (SASE:8130)</t>
+          <t>Walaa Cooperative Insurance Company (SASE:8060)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1847,28 +1847,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.187</v>
-      </c>
-      <c r="E12">
-        <v>-0.309</v>
+        <v>0.102</v>
       </c>
       <c r="G12">
-        <v>0.07328385899814471</v>
+        <v>-0.07812073204042611</v>
       </c>
       <c r="H12">
-        <v>0.07328385899814471</v>
+        <v>-0.07812073204042611</v>
       </c>
       <c r="I12">
-        <v>0.05435992578849722</v>
+        <v>-0.08003277792952745</v>
       </c>
       <c r="J12">
-        <v>0.02717996289424861</v>
+        <v>-0.08003277792952745</v>
       </c>
       <c r="K12">
-        <v>1.25</v>
+        <v>-31</v>
       </c>
       <c r="L12">
-        <v>0.02319109461966605</v>
+        <v>-0.08467631794591642</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1877,7 +1874,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1886,61 +1883,61 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>12.9</v>
+        <v>147.2</v>
       </c>
       <c r="V12">
-        <v>0.08872077028885832</v>
+        <v>0.4497402994194928</v>
       </c>
       <c r="W12">
-        <v>0.01920122887864823</v>
+        <v>-0.1339092872570194</v>
       </c>
       <c r="X12">
-        <v>0.04881336106789308</v>
+        <v>0.08262283442835908</v>
       </c>
       <c r="Y12">
-        <v>-0.02961213218924484</v>
+        <v>-0.2165321216853785</v>
       </c>
       <c r="Z12">
-        <v>0.9084780043822687</v>
+        <v>3.508721487444892</v>
       </c>
       <c r="AA12">
-        <v>0.02469239844935109</v>
+        <v>-0.2808127276212383</v>
       </c>
       <c r="AB12">
-        <v>0.04881336106789308</v>
+        <v>0.08242824693692233</v>
       </c>
       <c r="AC12">
-        <v>-0.02412096261854199</v>
+        <v>-0.3632409745581606</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG12">
-        <v>-12.9</v>
+        <v>-145.51</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.005136934253320769</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.008366750829248972</v>
       </c>
       <c r="AJ12">
-        <v>-0.09735849056603774</v>
+        <v>-0.8004290665053082</v>
       </c>
       <c r="AK12">
-        <v>-0.2411214953271028</v>
+        <v>-2.655776601569628</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1949,10 +1946,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>-0.0597173144876325</v>
       </c>
       <c r="AP12">
-        <v>-4.03125</v>
+        <v>5.141696113074205</v>
       </c>
     </row>
     <row r="13">
@@ -1963,7 +1960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Al-Etihad Cooperative Insurance Company (SASE:8170)</t>
+          <t>Wataniya Insurance Company (SASE:8300)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1972,25 +1969,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0218</v>
+        <v>0.0892</v>
       </c>
       <c r="G13">
-        <v>0.06153846153846153</v>
+        <v>-0.08223684210526316</v>
       </c>
       <c r="H13">
-        <v>0.06153846153846153</v>
+        <v>-0.08223684210526316</v>
       </c>
       <c r="I13">
-        <v>0.004244031830238727</v>
+        <v>-0.04618421052631579</v>
       </c>
       <c r="J13">
-        <v>0.002122015915119364</v>
+        <v>-0.04618421052631579</v>
       </c>
       <c r="K13">
-        <v>-2.96</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L13">
-        <v>-0.01570291777188329</v>
+        <v>-0.05407894736842106</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2014,73 +2011,67 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>121.7</v>
+        <v>16.1</v>
       </c>
       <c r="V13">
-        <v>0.5751417769376181</v>
+        <v>0.1117279666897988</v>
       </c>
       <c r="W13">
-        <v>-0.02013605442176871</v>
+        <v>-0.1462633451957295</v>
       </c>
       <c r="X13">
-        <v>0.04891902600674104</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y13">
-        <v>-0.06905508042850975</v>
+        <v>-0.2287059023942311</v>
       </c>
       <c r="Z13">
-        <v>4.926044007735327</v>
+        <v>6.468085106382978</v>
       </c>
       <c r="AA13">
-        <v>0.01045314378299274</v>
+        <v>-0.2987234042553191</v>
       </c>
       <c r="AB13">
-        <v>0.04881969919063821</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AC13">
-        <v>-0.03836655540764548</v>
+        <v>-0.3811659614538206</v>
       </c>
       <c r="AD13">
-        <v>0.829</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.829</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>-120.871</v>
+        <v>-16.1</v>
       </c>
       <c r="AH13">
-        <v>0.003902480358143191</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>0.005485380039568844</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-1.332220128073714</v>
+        <v>-0.12578125</v>
       </c>
       <c r="AK13">
-        <v>-4.107207176594516</v>
+        <v>-0.1963414634146342</v>
       </c>
       <c r="AL13">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>0.4657303370786516</v>
-      </c>
-      <c r="AO13">
-        <v>27.58620689655173</v>
+        <v>-0</v>
       </c>
       <c r="AP13">
-        <v>-67.90505617977529</v>
-      </c>
-      <c r="AQ13">
-        <v>27.58620689655173</v>
+        <v>2.761578044596913</v>
       </c>
     </row>
     <row r="14">
@@ -2091,7 +2082,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SABB Takaful Company (SASE:8080)</t>
+          <t>Gulf General Cooperative Insurance Company (SASE:8260)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2100,25 +2091,25 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.0177</v>
+        <v>0.123</v>
       </c>
       <c r="G14">
-        <v>-0.1683046683046683</v>
+        <v>-0.3017591339648173</v>
       </c>
       <c r="H14">
-        <v>-0.1683046683046683</v>
+        <v>-0.3017591339648173</v>
       </c>
       <c r="I14">
-        <v>-0.01665847665847666</v>
+        <v>-0.2760487144790257</v>
       </c>
       <c r="J14">
-        <v>-0.01665847665847666</v>
+        <v>-0.2760487144790257</v>
       </c>
       <c r="K14">
-        <v>-2.12</v>
+        <v>-21.7</v>
       </c>
       <c r="L14">
-        <v>-0.05208845208845209</v>
+        <v>-0.2936400541271989</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2142,55 +2133,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>14.8</v>
+        <v>4.08</v>
       </c>
       <c r="V14">
-        <v>0.0598705501618123</v>
+        <v>0.04503311258278146</v>
       </c>
       <c r="W14">
-        <v>-0.0265</v>
+        <v>-0.2035647279549719</v>
       </c>
       <c r="X14">
-        <v>0.04881336106789308</v>
+        <v>0.08251153748758348</v>
       </c>
       <c r="Y14">
-        <v>-0.07531336106789308</v>
+        <v>-0.2860762654425553</v>
       </c>
       <c r="Z14">
-        <v>1.654471544715447</v>
+        <v>4.247614668352686</v>
       </c>
       <c r="AA14">
-        <v>-0.0275609756097561</v>
+        <v>-1.172548568801012</v>
       </c>
       <c r="AB14">
-        <v>0.04881336106789308</v>
+        <v>0.08244921059976001</v>
       </c>
       <c r="AC14">
-        <v>-0.07637433667764917</v>
+        <v>-1.254997779400772</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AG14">
-        <v>-14.8</v>
+        <v>-3.901</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.001971821676819529</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>0.002113865303085771</v>
       </c>
       <c r="AJ14">
-        <v>-0.06368330464716007</v>
+        <v>-0.04499475195792339</v>
       </c>
       <c r="AK14">
-        <v>-0.2269938650306748</v>
+        <v>-0.04840010421965533</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2199,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="AN14">
-        <v>-0</v>
+        <v>-0.00873170731707317</v>
       </c>
       <c r="AP14">
-        <v>31.69164882226981</v>
+        <v>0.1902926829268293</v>
       </c>
     </row>
     <row r="15">
@@ -2213,7 +2204,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allianz Saudi Fransi Cooperative Insurance Company (SASE:8040)</t>
+          <t>Salama Cooperative Insurance Company (SASE:8050)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2222,25 +2213,25 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.0245</v>
+        <v>-0.0561</v>
       </c>
       <c r="G15">
-        <v>-0.07464671654197839</v>
+        <v>-0.2120743034055728</v>
       </c>
       <c r="H15">
-        <v>-0.07464671654197839</v>
+        <v>-0.2120743034055728</v>
       </c>
       <c r="I15">
-        <v>-0.085619285120532</v>
+        <v>-0.2662538699690403</v>
       </c>
       <c r="J15">
-        <v>-0.042809642560266</v>
+        <v>-0.2662538699690403</v>
       </c>
       <c r="K15">
-        <v>-2.26</v>
+        <v>-36</v>
       </c>
       <c r="L15">
-        <v>-0.01878636741479634</v>
+        <v>-0.2786377708978328</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2264,55 +2255,55 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>44.5</v>
+        <v>51.8</v>
       </c>
       <c r="V15">
-        <v>0.1077221011861535</v>
+        <v>1.501449275362319</v>
       </c>
       <c r="W15">
-        <v>-0.01170378042465044</v>
+        <v>-0.8035714285714286</v>
       </c>
       <c r="X15">
-        <v>0.04882876915932281</v>
+        <v>0.08711800332620187</v>
       </c>
       <c r="Y15">
-        <v>-0.06053254958397325</v>
+        <v>-0.8906894318976305</v>
       </c>
       <c r="Z15">
-        <v>1.098529814628801</v>
+        <v>7.250280583613916</v>
       </c>
       <c r="AA15">
-        <v>-0.04702766870605425</v>
+        <v>-1.930415263748597</v>
       </c>
       <c r="AB15">
-        <v>0.04881428838589406</v>
+        <v>0.08284104883308525</v>
       </c>
       <c r="AC15">
-        <v>-0.09584195709194832</v>
+        <v>-2.013256312581682</v>
       </c>
       <c r="AD15">
-        <v>0.236</v>
+        <v>4.62</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.236</v>
+        <v>4.62</v>
       </c>
       <c r="AG15">
-        <v>-44.264</v>
+        <v>-47.18</v>
       </c>
       <c r="AH15">
-        <v>0.0005709640582963981</v>
+        <v>0.1180981595092025</v>
       </c>
       <c r="AI15">
-        <v>0.00124580333199603</v>
+        <v>0.347107438016529</v>
       </c>
       <c r="AJ15">
-        <v>-0.1200099773340997</v>
+        <v>3.720820189274448</v>
       </c>
       <c r="AK15">
-        <v>-0.3054037644201579</v>
+        <v>1.225772928033255</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2321,10 +2312,10 @@
         <v>0</v>
       </c>
       <c r="AN15">
-        <v>-0.02554112554112554</v>
+        <v>-0.1346938775510204</v>
       </c>
       <c r="AP15">
-        <v>4.79047619047619</v>
+        <v>1.375510204081633</v>
       </c>
     </row>
     <row r="16">
@@ -2335,7 +2326,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Saudi Arabian Cooperative Insurance Company (SASE:8100)</t>
+          <t>The Mediterranean and Gulf Cooperative Insurance and Reinsurance Company (SASE:8030)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2344,25 +2335,25 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.00814</v>
+        <v>-0.0491</v>
       </c>
       <c r="G16">
-        <v>0.10079901659496</v>
+        <v>-0.06441374159820762</v>
       </c>
       <c r="H16">
-        <v>0.10079901659496</v>
+        <v>-0.06441374159820762</v>
       </c>
       <c r="I16">
-        <v>-0.03269821757836509</v>
+        <v>-0.1508588498879761</v>
       </c>
       <c r="J16">
-        <v>-0.03269821757836509</v>
+        <v>-0.1508588498879761</v>
       </c>
       <c r="K16">
-        <v>-7.44</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="L16">
-        <v>-0.04572833435771359</v>
+        <v>-0.1448842419716206</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2386,55 +2377,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>9.44</v>
+        <v>122.7</v>
       </c>
       <c r="V16">
-        <v>0.05385054192812321</v>
+        <v>0.5093399750933998</v>
       </c>
       <c r="W16">
-        <v>-0.08113413304252999</v>
+        <v>-0.3903420523138832</v>
       </c>
       <c r="X16">
-        <v>0.04881336106789308</v>
+        <v>0.0825976341140761</v>
       </c>
       <c r="Y16">
-        <v>-0.1299474941104231</v>
+        <v>-0.4729396864279594</v>
       </c>
       <c r="Z16">
-        <v>1.873344847438111</v>
+        <v>92.66435986159168</v>
       </c>
       <c r="AA16">
-        <v>-0.06125503742084053</v>
+        <v>-13.97923875432526</v>
       </c>
       <c r="AB16">
-        <v>0.04881336106789308</v>
+        <v>0.08243023847185627</v>
       </c>
       <c r="AC16">
-        <v>-0.1100683984887336</v>
+        <v>-14.06166899279711</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AG16">
-        <v>-9.44</v>
+        <v>-121.63</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.00442203578956069</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.004866512029835813</v>
       </c>
       <c r="AJ16">
-        <v>-0.05691547087905462</v>
+        <v>-1.019787037813365</v>
       </c>
       <c r="AK16">
-        <v>-0.1269499731038193</v>
+        <v>-1.251723783060616</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2443,10 +2434,10 @@
         <v>0</v>
       </c>
       <c r="AN16">
-        <v>-0</v>
+        <v>-0.01364795918367347</v>
       </c>
       <c r="AP16">
-        <v>2.140589569160998</v>
+        <v>1.55140306122449</v>
       </c>
     </row>
     <row r="17">
@@ -2457,7 +2448,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Walaa Cooperative Insurance Company (SASE:8060)</t>
+          <t>Amana Cooperative Insurance Company (SASE:8310)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2466,25 +2457,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.128</v>
+        <v>0.186</v>
       </c>
       <c r="G17">
-        <v>0.07782369146005511</v>
+        <v>-0.4922600619195047</v>
       </c>
       <c r="H17">
-        <v>0.07782369146005511</v>
+        <v>-0.4922600619195047</v>
       </c>
       <c r="I17">
-        <v>-0.008264462809917356</v>
+        <v>-0.2894736842105263</v>
       </c>
       <c r="J17">
-        <v>-0.008264462809917356</v>
+        <v>-0.2894736842105263</v>
       </c>
       <c r="K17">
-        <v>-6.95</v>
+        <v>-19</v>
       </c>
       <c r="L17">
-        <v>-0.02393250688705234</v>
+        <v>-0.2941176470588235</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2508,55 +2499,46 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>122.3</v>
+        <v>67.5</v>
       </c>
       <c r="V17">
-        <v>0.374235006119951</v>
+        <v>0.645933014354067</v>
       </c>
       <c r="W17">
-        <v>-0.02958705832269051</v>
+        <v>-8.296943231441048</v>
       </c>
       <c r="X17">
-        <v>0.04894953498652716</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="Y17">
-        <v>-0.07853659330921767</v>
-      </c>
-      <c r="Z17">
-        <v>9.674840085287846</v>
-      </c>
-      <c r="AA17">
-        <v>-0.07995735607675905</v>
+        <v>-8.379385788639549</v>
       </c>
       <c r="AB17">
-        <v>0.04882152002401803</v>
-      </c>
-      <c r="AC17">
-        <v>-0.1287788761007771</v>
+        <v>0.08244255719850152</v>
       </c>
       <c r="AD17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>-120.65</v>
+        <v>-67.5</v>
       </c>
       <c r="AH17">
-        <v>0.005023595676663115</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>0.007076989062835084</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>-0.5852534562211981</v>
+        <v>-1.824324324324324</v>
       </c>
       <c r="AK17">
-        <v>-1.088407758231845</v>
+        <v>10.07462686567164</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2565,10 +2547,10 @@
         <v>0</v>
       </c>
       <c r="AN17">
-        <v>-0.4342105263157895</v>
+        <v>-0</v>
       </c>
       <c r="AP17">
-        <v>31.75</v>
+        <v>3.708791208791209</v>
       </c>
     </row>
     <row r="18">
@@ -2579,7 +2561,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Mediterranean and Gulf Cooperative Insurance and Reinsurance Company (SASE:8030)</t>
+          <t>Allied Cooperative Insurance Group (SASE:8150)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2588,25 +2570,25 @@
         </is>
       </c>
       <c r="D18">
-        <v>-0.12</v>
+        <v>0.059</v>
       </c>
       <c r="G18">
-        <v>0.0364963503649635</v>
+        <v>-0.1871988988300069</v>
       </c>
       <c r="H18">
-        <v>0.0364963503649635</v>
+        <v>-0.1871988988300069</v>
       </c>
       <c r="I18">
-        <v>0.00413625304136253</v>
+        <v>-0.2023399862353751</v>
       </c>
       <c r="J18">
-        <v>0.002068126520681265</v>
+        <v>-0.2023399862353751</v>
       </c>
       <c r="K18">
-        <v>-1.51</v>
+        <v>-28.6</v>
       </c>
       <c r="L18">
-        <v>-0.00333996903339969</v>
+        <v>-0.1968341362697866</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2630,55 +2612,46 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>67.40000000000001</v>
+        <v>108.9</v>
       </c>
       <c r="V18">
-        <v>0.140270551508845</v>
+        <v>1.302631578947369</v>
       </c>
       <c r="W18">
-        <v>-0.007490079365079365</v>
+        <v>-0.9533333333333334</v>
       </c>
       <c r="X18">
-        <v>0.0489469515766824</v>
+        <v>0.08272863520501803</v>
       </c>
       <c r="Y18">
-        <v>-0.05643703094176176</v>
-      </c>
-      <c r="Z18">
-        <v>-41.78373382624766</v>
-      </c>
-      <c r="AA18">
-        <v>-0.08641404805914966</v>
+        <v>-1.036061968538351</v>
       </c>
       <c r="AB18">
-        <v>0.04882136600010711</v>
-      </c>
-      <c r="AC18">
-        <v>-0.1352354140592568</v>
+        <v>0.08241991681153951</v>
       </c>
       <c r="AD18">
-        <v>2.38</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>2.38</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="AG18">
-        <v>-65.02000000000001</v>
+        <v>-108.215</v>
       </c>
       <c r="AH18">
-        <v>0.004928760768721007</v>
+        <v>0.008127187518538293</v>
       </c>
       <c r="AI18">
-        <v>0.01183020180932498</v>
+        <v>0.01635430344992241</v>
       </c>
       <c r="AJ18">
-        <v>-0.1564936940406277</v>
+        <v>4.396303067235424</v>
       </c>
       <c r="AK18">
-        <v>-0.4860218268799522</v>
+        <v>1.614787734089383</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -2687,10 +2660,10 @@
         <v>0</v>
       </c>
       <c r="AN18">
-        <v>0.6449864498644986</v>
+        <v>-0.02362068965517242</v>
       </c>
       <c r="AP18">
-        <v>-17.62059620596206</v>
+        <v>3.731551724137931</v>
       </c>
     </row>
     <row r="19">
@@ -2701,7 +2674,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alinma Tokio Marine Company (SASE:8312)</t>
+          <t>Gulf Union Alahlia Cooperative Insurance Company (SASE:8120)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2710,25 +2683,25 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.08289999999999999</v>
+        <v>0.154</v>
       </c>
       <c r="G19">
-        <v>0.01515030060120241</v>
+        <v>-0.2678018575851394</v>
       </c>
       <c r="H19">
-        <v>0.01515030060120241</v>
+        <v>-0.2678018575851394</v>
       </c>
       <c r="I19">
-        <v>-0.06343650879102794</v>
+        <v>-0.06702786377708979</v>
       </c>
       <c r="J19">
-        <v>-0.06343650879102794</v>
+        <v>-0.06702786377708979</v>
       </c>
       <c r="K19">
-        <v>-4.3</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L19">
-        <v>-0.08617234468937876</v>
+        <v>-0.07128482972136224</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2752,439 +2725,64 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>50.6</v>
+        <v>24.4</v>
       </c>
       <c r="V19">
-        <v>0.2016739736946991</v>
+        <v>0.2343900096061479</v>
       </c>
       <c r="W19">
-        <v>-0.07747747747747748</v>
+        <v>-0.233756345177665</v>
       </c>
       <c r="X19">
-        <v>0.04893777763420876</v>
+        <v>0.08305967385744673</v>
       </c>
       <c r="Y19">
-        <v>-0.1264152551116862</v>
-      </c>
-      <c r="Z19">
-        <v>4.244132379879055</v>
-      </c>
-      <c r="AA19">
-        <v>-0.269232941026484</v>
+        <v>-0.3168160190351117</v>
       </c>
       <c r="AB19">
-        <v>0.04883778227679723</v>
-      </c>
-      <c r="AC19">
-        <v>-0.3180707233032812</v>
+        <v>0.08239417323749658</v>
       </c>
       <c r="AD19">
-        <v>1.14</v>
+        <v>1.84</v>
       </c>
       <c r="AE19">
-        <v>0.01740894336146717</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.157408943361467</v>
+        <v>1.84</v>
       </c>
       <c r="AG19">
-        <v>-49.44259105663853</v>
+        <v>-22.56</v>
       </c>
       <c r="AH19">
-        <v>0.004591846548821513</v>
+        <v>0.0173683216915235</v>
       </c>
       <c r="AI19">
-        <v>0.02210592477205116</v>
+        <v>0.02073473067387874</v>
       </c>
       <c r="AJ19">
-        <v>-0.2454245357168225</v>
+        <v>-0.2766740250183959</v>
       </c>
       <c r="AK19">
-        <v>-28.13379961642146</v>
+        <v>-0.3506372396642835</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="AN19">
-        <v>-0.5017605633802816</v>
+        <v>-0.2893081761006289</v>
+      </c>
+      <c r="AO19">
+        <v>-56.23376623376623</v>
       </c>
       <c r="AP19">
-        <v>21.7617038101402</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Salama Cooperative Insurance Company (SASE:8050)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>0.00894</v>
-      </c>
-      <c r="G20">
-        <v>0.03438320209973753</v>
-      </c>
-      <c r="H20">
-        <v>0.03438320209973753</v>
-      </c>
-      <c r="I20">
-        <v>-0.08223972003499563</v>
-      </c>
-      <c r="J20">
-        <v>-0.08223972003499563</v>
-      </c>
-      <c r="K20">
-        <v>-10.6</v>
-      </c>
-      <c r="L20">
-        <v>-0.09273840769903761</v>
-      </c>
-      <c r="M20">
-        <v>-0</v>
-      </c>
-      <c r="N20">
-        <v>-0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>-0</v>
-      </c>
-      <c r="Q20">
-        <v>-0</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>32.4</v>
-      </c>
-      <c r="V20">
-        <v>0.2862190812720848</v>
-      </c>
-      <c r="W20">
-        <v>-0.1920289855072464</v>
-      </c>
-      <c r="X20">
-        <v>0.05010471383812615</v>
-      </c>
-      <c r="Y20">
-        <v>-0.2421336993453725</v>
-      </c>
-      <c r="Z20">
-        <v>9.613120269133725</v>
-      </c>
-      <c r="AA20">
-        <v>-0.7905803195962994</v>
-      </c>
-      <c r="AB20">
-        <v>0.0488875708722323</v>
-      </c>
-      <c r="AC20">
-        <v>-0.8394678904685317</v>
-      </c>
-      <c r="AD20">
-        <v>5.42</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>5.42</v>
-      </c>
-      <c r="AG20">
-        <v>-26.98</v>
-      </c>
-      <c r="AH20">
-        <v>0.04569212611701231</v>
-      </c>
-      <c r="AI20">
-        <v>0.1079251294305058</v>
-      </c>
-      <c r="AJ20">
-        <v>-0.3129204360937137</v>
-      </c>
-      <c r="AK20">
-        <v>-1.514029180695847</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-      <c r="AN20">
-        <v>-0.6800501882057717</v>
-      </c>
-      <c r="AP20">
-        <v>3.385194479297365</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Amana Cooperative Insurance Company (SASE:8310)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>-0.0411</v>
-      </c>
-      <c r="G21">
-        <v>-0.2079207920792079</v>
-      </c>
-      <c r="H21">
-        <v>-0.2079207920792079</v>
-      </c>
-      <c r="I21">
-        <v>-0.4582743988684582</v>
-      </c>
-      <c r="J21">
-        <v>-0.4582743988684582</v>
-      </c>
-      <c r="K21">
-        <v>-32.7</v>
-      </c>
-      <c r="L21">
-        <v>-0.4625176803394626</v>
-      </c>
-      <c r="M21">
-        <v>-0</v>
-      </c>
-      <c r="N21">
-        <v>-0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>-0</v>
-      </c>
-      <c r="Q21">
-        <v>-0</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>21.2</v>
-      </c>
-      <c r="V21">
-        <v>0.1780016792611251</v>
-      </c>
-      <c r="W21">
-        <v>-0.7622377622377623</v>
-      </c>
-      <c r="X21">
-        <v>0.04881336106789308</v>
-      </c>
-      <c r="Y21">
-        <v>-0.8110511233056554</v>
-      </c>
-      <c r="Z21">
-        <v>2.195652173913043</v>
-      </c>
-      <c r="AA21">
-        <v>-1.006211180124224</v>
-      </c>
-      <c r="AB21">
-        <v>0.04881336106789308</v>
-      </c>
-      <c r="AC21">
-        <v>-1.055024541192117</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>-21.2</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>-0.2165474974463739</v>
-      </c>
-      <c r="AK21">
-        <v>1.121099947117927</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>-0</v>
-      </c>
-      <c r="AP21">
-        <v>0.664576802507837</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Gulf Union Alahlia Cooperative Insurance Company (SASE:8120)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>0.319</v>
-      </c>
-      <c r="G22">
-        <v>-0.06088004822182037</v>
-      </c>
-      <c r="H22">
-        <v>-0.06088004822182037</v>
-      </c>
-      <c r="I22">
-        <v>-0.2477396021699819</v>
-      </c>
-      <c r="J22">
-        <v>-0.2477396021699819</v>
-      </c>
-      <c r="K22">
-        <v>-42.6</v>
-      </c>
-      <c r="L22">
-        <v>-0.2567811934900542</v>
-      </c>
-      <c r="M22">
-        <v>-0</v>
-      </c>
-      <c r="N22">
-        <v>-0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>-0</v>
-      </c>
-      <c r="Q22">
-        <v>-0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>32.2</v>
-      </c>
-      <c r="V22">
-        <v>0.3184965380811078</v>
-      </c>
-      <c r="W22">
-        <v>-1.136</v>
-      </c>
-      <c r="X22">
-        <v>0.04934690585235034</v>
-      </c>
-      <c r="Y22">
-        <v>-1.18534690585235</v>
-      </c>
-      <c r="Z22">
-        <v>54.75247524752474</v>
-      </c>
-      <c r="AA22">
-        <v>-13.56435643564356</v>
-      </c>
-      <c r="AB22">
-        <v>0.0488448669214538</v>
-      </c>
-      <c r="AC22">
-        <v>-13.61320130256501</v>
-      </c>
-      <c r="AD22">
-        <v>2</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>2</v>
-      </c>
-      <c r="AG22">
-        <v>-30.2</v>
-      </c>
-      <c r="AH22">
-        <v>0.01939864209505335</v>
-      </c>
-      <c r="AI22">
-        <v>0.04830917874396135</v>
-      </c>
-      <c r="AJ22">
-        <v>-0.4259520451339917</v>
-      </c>
-      <c r="AK22">
-        <v>-3.282608695652176</v>
-      </c>
-      <c r="AL22">
-        <v>0.075</v>
-      </c>
-      <c r="AM22">
-        <v>0.075</v>
-      </c>
-      <c r="AN22">
-        <v>-0.04938271604938271</v>
-      </c>
-      <c r="AO22">
-        <v>-548</v>
-      </c>
-      <c r="AP22">
-        <v>0.7456790123456791</v>
-      </c>
-      <c r="AQ22">
-        <v>-548</v>
+        <v>3.547169811320754</v>
+      </c>
+      <c r="AQ19">
+        <v>-56.23376623376623</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AQ20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0572</v>
+        <v>0.1345</v>
       </c>
       <c r="E2">
-        <v>-0.174</v>
+        <v>0.07455000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.01480988360933219</v>
+        <v>0.008810557101750082</v>
       </c>
       <c r="H2">
-        <v>-0.01480988360933219</v>
+        <v>0.008810557101750082</v>
       </c>
       <c r="I2">
-        <v>-0.01886348962604917</v>
+        <v>0.07393862918062173</v>
       </c>
       <c r="J2">
-        <v>-0.01595400023251066</v>
+        <v>0.06246284366774955</v>
       </c>
       <c r="K2">
-        <v>-135.393</v>
+        <v>526.371</v>
       </c>
       <c r="L2">
-        <v>-0.02362590957474654</v>
+        <v>0.06207497995188452</v>
       </c>
       <c r="M2">
-        <v>0.028</v>
+        <v>40.848</v>
       </c>
       <c r="N2">
-        <v>4.809922182330407e-06</v>
+        <v>0.003705605399472028</v>
       </c>
       <c r="O2">
-        <v>-0.0002068053739853611</v>
+        <v>0.07760305943906484</v>
       </c>
       <c r="P2">
-        <v>0.028</v>
+        <v>40.07</v>
       </c>
       <c r="Q2">
-        <v>4.809922182330407e-06</v>
+        <v>0.003635027623306995</v>
       </c>
       <c r="R2">
-        <v>-0.0002068053739853611</v>
+        <v>0.07612501448598043</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.01904622013317666</v>
       </c>
       <c r="U2">
-        <v>1412.63</v>
+        <v>1999.85</v>
       </c>
       <c r="V2">
-        <v>0.2426657275866215</v>
+        <v>0.1814202643491513</v>
       </c>
       <c r="W2">
-        <v>-0.1339092872570194</v>
+        <v>0.1632793819139712</v>
       </c>
       <c r="X2">
-        <v>0.0825976341140761</v>
+        <v>0.07392432751336113</v>
       </c>
       <c r="Y2">
-        <v>-0.2165069213710956</v>
+        <v>0.08935505440061005</v>
       </c>
       <c r="Z2">
-        <v>3.734892802769609</v>
+        <v>5.340057420920284</v>
       </c>
       <c r="AA2">
-        <v>-0.2192038730500269</v>
+        <v>0.4833698881934297</v>
       </c>
       <c r="AB2">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC2">
-        <v>-0.3016464302485284</v>
+        <v>0.4095192677399522</v>
       </c>
       <c r="AD2">
-        <v>27.118</v>
+        <v>34.827</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>27.118</v>
+        <v>34.827</v>
       </c>
       <c r="AG2">
-        <v>-1385.512</v>
+        <v>-1965.023</v>
       </c>
       <c r="AH2">
-        <v>0.004636809475656494</v>
+        <v>0.00314944836498984</v>
       </c>
       <c r="AI2">
-        <v>0.009479802895048886</v>
+        <v>0.008679567763656169</v>
       </c>
       <c r="AJ2">
-        <v>-0.31234856129283</v>
+        <v>-0.2169312110901444</v>
       </c>
       <c r="AK2">
-        <v>-0.9568598417931765</v>
+        <v>-0.9763230761816228</v>
       </c>
       <c r="AL2">
-        <v>0.27</v>
+        <v>76.261</v>
       </c>
       <c r="AM2">
-        <v>0.27</v>
+        <v>76.261</v>
       </c>
       <c r="AN2">
-        <v>-0.3381718418755456</v>
+        <v>0.05237930515867047</v>
       </c>
       <c r="AO2">
-        <v>-400.374074074074</v>
+        <v>8.221371343150498</v>
       </c>
       <c r="AP2">
-        <v>17.27786507045766</v>
+        <v>-2.955366220484283</v>
       </c>
       <c r="AQ2">
-        <v>-400.374074074074</v>
+        <v>8.221371343150498</v>
       </c>
     </row>
     <row r="3">
@@ -722,28 +722,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0524</v>
+        <v>0.0992</v>
       </c>
       <c r="E3">
-        <v>-0.201</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="G3">
-        <v>0.0520951302378256</v>
+        <v>0.04718516108037748</v>
       </c>
       <c r="H3">
-        <v>0.0520951302378256</v>
+        <v>0.04718516108037748</v>
       </c>
       <c r="I3">
-        <v>0.03669309173272934</v>
+        <v>0.1060852587048487</v>
       </c>
       <c r="J3">
-        <v>0.01993110705981761</v>
+        <v>0.09172294675711531</v>
       </c>
       <c r="K3">
-        <v>5.22</v>
+        <v>28.1</v>
       </c>
       <c r="L3">
-        <v>0.01970554926387316</v>
+        <v>0.09144158802473154</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,73 +767,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>82</v>
+        <v>18.7</v>
       </c>
       <c r="V3">
-        <v>0.4527885146327996</v>
+        <v>0.08488424875170221</v>
       </c>
       <c r="W3">
-        <v>0.03473053892215568</v>
+        <v>0.196366177498253</v>
       </c>
       <c r="X3">
-        <v>0.0827760817659379</v>
+        <v>0.07404976456365171</v>
       </c>
       <c r="Y3">
-        <v>-0.04804554284378221</v>
-      </c>
-      <c r="Z3">
-        <v>9.383966842608658</v>
-      </c>
-      <c r="AA3">
-        <v>0.1870328477858118</v>
+        <v>0.1223164129346013</v>
       </c>
       <c r="AB3">
-        <v>0.08241619739254631</v>
-      </c>
-      <c r="AC3">
-        <v>0.1046166503932654</v>
+        <v>0.07382853034443301</v>
       </c>
       <c r="AD3">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AG3">
-        <v>-80.27</v>
+        <v>-17.16</v>
       </c>
       <c r="AH3">
-        <v>0.009462342066400483</v>
+        <v>0.006941940137035701</v>
       </c>
       <c r="AI3">
-        <v>0.01146226727622077</v>
+        <v>0.00888427368178147</v>
       </c>
       <c r="AJ3">
-        <v>-0.7960924328076961</v>
+        <v>-0.08447376193757999</v>
       </c>
       <c r="AK3">
-        <v>-1.164514725083418</v>
+        <v>-0.1109674081738231</v>
       </c>
       <c r="AL3">
-        <v>0.116</v>
+        <v>0.073</v>
       </c>
       <c r="AM3">
-        <v>0.116</v>
+        <v>0.073</v>
       </c>
       <c r="AN3">
-        <v>0.1632075471698113</v>
+        <v>0.04597014925373134</v>
       </c>
       <c r="AO3">
-        <v>83.79310344827586</v>
+        <v>446.5753424657535</v>
       </c>
       <c r="AP3">
-        <v>-7.572641509433963</v>
+        <v>-0.5122388059701493</v>
       </c>
       <c r="AQ3">
-        <v>83.79310344827586</v>
+        <v>446.5753424657535</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alinma Tokio Marine Company (SASE:8312)</t>
+          <t>The Mediterranean and Gulf Cooperative Insurance and Reinsurance Company (SASE:8030)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0572</v>
+        <v>0.0827</v>
       </c>
       <c r="G4">
-        <v>-0.03350427350427351</v>
+        <v>-0.1080977357042344</v>
       </c>
       <c r="H4">
-        <v>-0.03350427350427351</v>
+        <v>-0.1080977357042344</v>
       </c>
       <c r="I4">
-        <v>0.009709401709401709</v>
+        <v>0.001893309453754637</v>
       </c>
       <c r="J4">
-        <v>0.004854700854700854</v>
+        <v>0.0009466547268773187</v>
       </c>
       <c r="K4">
-        <v>-0.139</v>
+        <v>-0.259</v>
       </c>
       <c r="L4">
-        <v>-0.002376068376068376</v>
+        <v>-0.0003313291544070615</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,55 +886,46 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>36</v>
+        <v>111.2</v>
       </c>
       <c r="V4">
-        <v>0.3757828810020877</v>
+        <v>0.2757936507936508</v>
       </c>
       <c r="W4">
-        <v>-0.00271484375</v>
+        <v>-0.001183729433272395</v>
       </c>
       <c r="X4">
-        <v>0.0826903813228855</v>
+        <v>0.07405334251231205</v>
       </c>
       <c r="Y4">
-        <v>-0.0854052250728855</v>
-      </c>
-      <c r="Z4">
-        <v>33.62068965517238</v>
-      </c>
-      <c r="AA4">
-        <v>0.1632183908045975</v>
+        <v>-0.07523707194558445</v>
       </c>
       <c r="AB4">
-        <v>0.08246633916140199</v>
-      </c>
-      <c r="AC4">
-        <v>0.0807520516431955</v>
+        <v>0.07386093583651177</v>
       </c>
       <c r="AD4">
-        <v>0.68</v>
+        <v>2.87</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.68</v>
+        <v>2.87</v>
       </c>
       <c r="AG4">
-        <v>-35.32</v>
+        <v>-108.33</v>
       </c>
       <c r="AH4">
-        <v>0.007048092868988391</v>
+        <v>0.007067746940182727</v>
       </c>
       <c r="AI4">
-        <v>0.01313248358439552</v>
+        <v>0.01263927423261549</v>
       </c>
       <c r="AJ4">
-        <v>-0.5839947089947091</v>
+        <v>-0.3673822362396988</v>
       </c>
       <c r="AK4">
-        <v>-2.238276299112801</v>
+        <v>-0.9349270734443774</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -952,10 +934,10 @@
         <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.422360248447205</v>
+        <v>0.767379679144385</v>
       </c>
       <c r="AP4">
-        <v>-21.93788819875776</v>
+        <v>-28.96524064171123</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Company for Cooperative Insurance (SASE:8010)</t>
+          <t>Allied Cooperative Insurance Group (SASE:8150)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,103 +957,91 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0555</v>
+        <v>0.164</v>
       </c>
       <c r="E5">
-        <v>-0.147</v>
+        <v>0.9309999999999999</v>
       </c>
       <c r="G5">
-        <v>0.03754792152146133</v>
+        <v>-0.02137468566638726</v>
       </c>
       <c r="H5">
-        <v>0.03754792152146133</v>
+        <v>-0.02137468566638726</v>
       </c>
       <c r="I5">
-        <v>0.03976546643614223</v>
+        <v>0.07502095557418273</v>
       </c>
       <c r="J5">
-        <v>0.03170139975420827</v>
+        <v>0.06743503772003352</v>
       </c>
       <c r="K5">
-        <v>85.59999999999999</v>
+        <v>16.1</v>
       </c>
       <c r="L5">
-        <v>0.03217319401638728</v>
+        <v>0.067476948868399</v>
       </c>
       <c r="M5">
-        <v>0.028</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>1.045634476062439e-05</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.0003271028037383178</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.028</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>1.045634476062439e-05</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.0003271028037383178</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>371.9</v>
+        <v>180.6</v>
       </c>
       <c r="V5">
-        <v>0.1388826648741504</v>
+        <v>1.673772011121408</v>
       </c>
       <c r="W5">
-        <v>0.1062562065541211</v>
+        <v>0.3907766990291262</v>
       </c>
       <c r="X5">
-        <v>0.08244255719850152</v>
+        <v>0.07391012883570397</v>
       </c>
       <c r="Y5">
-        <v>0.02381364935561962</v>
-      </c>
-      <c r="Z5">
-        <v>4.141011673151751</v>
-      </c>
-      <c r="AA5">
-        <v>0.1312758664374265</v>
+        <v>0.3168665701934222</v>
       </c>
       <c r="AB5">
-        <v>0.08244255719850152</v>
-      </c>
-      <c r="AC5">
-        <v>0.04883330923892495</v>
+        <v>0.07384644486517021</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="AG5">
-        <v>-371.9</v>
+        <v>-180.383</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.002007084917265555</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.003448988349730597</v>
       </c>
       <c r="AJ5">
-        <v>-0.1612819289648293</v>
+        <v>2.488624918946512</v>
       </c>
       <c r="AK5">
-        <v>-0.7625589501742873</v>
+        <v>1.532787233500166</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1080,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.01179347826086957</v>
       </c>
       <c r="AP5">
-        <v>-3.214347450302506</v>
+        <v>-9.803423913043478</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aljazira Takaful Taawuni Company (SASE:8012)</t>
+          <t>Salama Cooperative Insurance Company (SASE:8050)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,28 +1073,28 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.29</v>
+        <v>0.00083</v>
       </c>
       <c r="E6">
-        <v>-0.0326</v>
+        <v>0.173</v>
       </c>
       <c r="G6">
-        <v>0.168</v>
+        <v>-0.06968641114982578</v>
       </c>
       <c r="H6">
-        <v>0.168</v>
+        <v>-0.06968641114982578</v>
       </c>
       <c r="I6">
-        <v>0.1691764705882353</v>
+        <v>0.09457441513190643</v>
       </c>
       <c r="J6">
-        <v>0.1620235294117647</v>
+        <v>0.09059233449477352</v>
       </c>
       <c r="K6">
-        <v>6.88</v>
+        <v>18.2</v>
       </c>
       <c r="L6">
-        <v>0.1618823529411765</v>
+        <v>0.09059233449477351</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1148,55 +1118,46 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>30.6</v>
+        <v>88.8</v>
       </c>
       <c r="V6">
-        <v>0.1421933085501859</v>
+        <v>0.815426997245179</v>
       </c>
       <c r="W6">
-        <v>0.03182238667900093</v>
+        <v>2.094361334867664</v>
       </c>
       <c r="X6">
-        <v>0.08257137575023242</v>
+        <v>0.07524171710454011</v>
       </c>
       <c r="Y6">
-        <v>-0.05074898907123149</v>
-      </c>
-      <c r="Z6">
-        <v>0.3600474415452389</v>
-      </c>
-      <c r="AA6">
-        <v>0.05833615723483565</v>
+        <v>2.019119617763124</v>
       </c>
       <c r="AB6">
-        <v>0.08243231666977378</v>
-      </c>
-      <c r="AC6">
-        <v>-0.02409615943493813</v>
+        <v>0.07390180654923736</v>
       </c>
       <c r="AD6">
-        <v>0.794</v>
+        <v>5.39</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.794</v>
+        <v>5.39</v>
       </c>
       <c r="AG6">
-        <v>-29.806</v>
+        <v>-83.41</v>
       </c>
       <c r="AH6">
-        <v>0.003676028037815865</v>
+        <v>0.04716073147256977</v>
       </c>
       <c r="AI6">
-        <v>0.003544737805476933</v>
+        <v>0.1628890903596253</v>
       </c>
       <c r="AJ6">
-        <v>-0.1607711144912996</v>
+        <v>-3.272263632797174</v>
       </c>
       <c r="AK6">
-        <v>-0.1541206035347529</v>
+        <v>1.497217734697541</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1205,10 +1166,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.09418742586002374</v>
+        <v>0.275</v>
       </c>
       <c r="AP6">
-        <v>-3.53570581257414</v>
+        <v>-4.255612244897959</v>
       </c>
     </row>
     <row r="7">
@@ -1219,7 +1180,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Al Rajhi Company for Cooperative Insurance (SASE:8230)</t>
+          <t>Amana Cooperative Insurance Company (SASE:8310)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,28 +1189,25 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.00681</v>
-      </c>
-      <c r="E7">
-        <v>-0.221</v>
+        <v>0.291</v>
       </c>
       <c r="G7">
-        <v>0.05063098677208453</v>
+        <v>-0.1682692307692308</v>
       </c>
       <c r="H7">
-        <v>0.05063098677208453</v>
+        <v>-0.1682692307692308</v>
       </c>
       <c r="I7">
-        <v>0.01885358065987532</v>
+        <v>0.1794871794871795</v>
       </c>
       <c r="J7">
-        <v>0.01885358065987532</v>
+        <v>0.1560683760683761</v>
       </c>
       <c r="K7">
-        <v>13</v>
+        <v>9.17</v>
       </c>
       <c r="L7">
-        <v>0.01976585069180477</v>
+        <v>0.1469551282051282</v>
       </c>
       <c r="M7">
         <v>-0</v>
@@ -1273,55 +1231,46 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>198.3</v>
+        <v>63.2</v>
       </c>
       <c r="V7">
-        <v>0.2081452713341031</v>
+        <v>0.4218958611481976</v>
       </c>
       <c r="W7">
-        <v>0.03716409376786735</v>
+        <v>0.1508223684210526</v>
       </c>
       <c r="X7">
-        <v>0.08287866210511402</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y7">
-        <v>-0.04571456833724667</v>
-      </c>
-      <c r="Z7">
-        <v>2.53938223938224</v>
-      </c>
-      <c r="AA7">
-        <v>0.04787644787644788</v>
+        <v>0.07696863743242585</v>
       </c>
       <c r="AB7">
-        <v>0.08240819006825183</v>
-      </c>
-      <c r="AC7">
-        <v>-0.03453174219180395</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AD7">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>11.9</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>-186.4</v>
+        <v>-63.2</v>
       </c>
       <c r="AH7">
-        <v>0.0123367198838897</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.03277334067749932</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.2432467701944408</v>
+        <v>-0.7297921478060045</v>
       </c>
       <c r="AK7">
-        <v>-1.131067961165049</v>
+        <v>-5.693693693693697</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1330,10 +1279,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>0.7041420118343196</v>
+        <v>0</v>
       </c>
       <c r="AP7">
-        <v>-11.02958579881657</v>
+        <v>-5.401709401709402</v>
       </c>
     </row>
     <row r="8">
@@ -1344,7 +1293,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chubb Arabia Cooperative Insurance Company (SASE:8240)</t>
+          <t>Arabia Insurance Cooperative Company (SASE:8160)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1353,28 +1302,28 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.006770000000000001</v>
+        <v>0.242</v>
       </c>
       <c r="E8">
-        <v>-0.449</v>
+        <v>0.748</v>
       </c>
       <c r="G8">
-        <v>0.1065902578796562</v>
+        <v>0.02113739305485657</v>
       </c>
       <c r="H8">
-        <v>0.1065902578796562</v>
+        <v>0.02113739305485657</v>
       </c>
       <c r="I8">
-        <v>0.06361031518624642</v>
+        <v>0.132360342224459</v>
       </c>
       <c r="J8">
-        <v>0.03180515759312321</v>
+        <v>0.1157411064294597</v>
       </c>
       <c r="K8">
-        <v>0.55</v>
+        <v>19.5</v>
       </c>
       <c r="L8">
-        <v>0.01575931232091691</v>
+        <v>0.09813789632611979</v>
       </c>
       <c r="M8">
         <v>-0</v>
@@ -1401,64 +1350,70 @@
         <v>43.4</v>
       </c>
       <c r="V8">
-        <v>0.3508488278092158</v>
+        <v>0.2009259259259259</v>
       </c>
       <c r="W8">
-        <v>0.005729166666666667</v>
+        <v>0.3356282271944923</v>
       </c>
       <c r="X8">
-        <v>0.08244255719850152</v>
+        <v>0.07402770135723703</v>
       </c>
       <c r="Y8">
-        <v>-0.07671339053183485</v>
+        <v>0.2616005258372552</v>
       </c>
       <c r="Z8">
-        <v>0.527190332326284</v>
+        <v>26.00785340314133</v>
       </c>
       <c r="AA8">
-        <v>0.01676737160120846</v>
+        <v>3.010177728734766</v>
       </c>
       <c r="AB8">
-        <v>0.08244255719850152</v>
+        <v>0.07387318052147721</v>
       </c>
       <c r="AC8">
-        <v>-0.06567518559729306</v>
+        <v>2.936304548213288</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG8">
-        <v>-43.4</v>
+        <v>-42.06</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.006165455047391185</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.009119368449707364</v>
       </c>
       <c r="AJ8">
-        <v>-0.5404732254047322</v>
+        <v>-0.2418075198344256</v>
       </c>
       <c r="AK8">
-        <v>-0.8314176245210728</v>
+        <v>-0.4062198184276608</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>0.04908424908424908</v>
+      </c>
+      <c r="AO8">
+        <v>6.575</v>
       </c>
       <c r="AP8">
-        <v>-18.15899581589958</v>
+        <v>-1.540659340659341</v>
+      </c>
+      <c r="AQ8">
+        <v>6.575</v>
       </c>
     </row>
     <row r="9">
@@ -1469,7 +1424,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arabia Insurance Cooperative Company (SASE:8160)</t>
+          <t>Al Rajhi Company for Cooperative Insurance (SASE:8230)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1478,25 +1433,28 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0712</v>
+        <v>0.0236</v>
+      </c>
+      <c r="E9">
+        <v>0.0375</v>
       </c>
       <c r="G9">
-        <v>0.007662100456621004</v>
+        <v>0.03539530267945749</v>
       </c>
       <c r="H9">
-        <v>0.007662100456621004</v>
+        <v>0.03539530267945749</v>
       </c>
       <c r="I9">
-        <v>0.001378995433789954</v>
+        <v>0.1055243135957658</v>
       </c>
       <c r="J9">
-        <v>0.0006894977168949772</v>
+        <v>0.1030303859480077</v>
       </c>
       <c r="K9">
-        <v>-0.914</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L9">
-        <v>-0.00834703196347032</v>
+        <v>0.07288565442716947</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1505,7 +1463,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1514,73 +1472,79 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>50.8</v>
+        <v>252.2</v>
       </c>
       <c r="V9">
-        <v>0.3602836879432624</v>
+        <v>0.1326460842581392</v>
       </c>
       <c r="W9">
-        <v>-0.01538720538720539</v>
+        <v>0.1882118451025057</v>
       </c>
       <c r="X9">
-        <v>0.08252674709607594</v>
+        <v>0.07401744904005425</v>
       </c>
       <c r="Y9">
-        <v>-0.09791395248328133</v>
+        <v>0.1141943960624514</v>
       </c>
       <c r="Z9">
-        <v>3.587223587223588</v>
+        <v>5.503033980582526</v>
       </c>
       <c r="AA9">
-        <v>0.002473382473382474</v>
+        <v>0.5669797149044186</v>
       </c>
       <c r="AB9">
-        <v>0.08245798695575578</v>
+        <v>0.073832660479863</v>
       </c>
       <c r="AC9">
-        <v>-0.07998460448237331</v>
+        <v>0.4931470544245555</v>
       </c>
       <c r="AD9">
-        <v>0.34</v>
+        <v>11.1</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.34</v>
+        <v>11.1</v>
       </c>
       <c r="AG9">
-        <v>-50.45999999999999</v>
+        <v>-241.1</v>
       </c>
       <c r="AH9">
-        <v>0.002405546908164709</v>
+        <v>0.005804225057519347</v>
       </c>
       <c r="AI9">
-        <v>0.005817932922655715</v>
+        <v>0.0253598355037697</v>
       </c>
       <c r="AJ9">
-        <v>-0.5573227302849568</v>
+        <v>-0.1452234670521624</v>
       </c>
       <c r="AK9">
-        <v>-6.60471204188481</v>
+        <v>-1.299730458221024</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="AN9">
-        <v>0.3732162458836444</v>
+        <v>0.1085043988269795</v>
+      </c>
+      <c r="AO9">
+        <v>3.393617021276596</v>
       </c>
       <c r="AP9">
-        <v>-55.38968166849615</v>
+        <v>-2.356793743890518</v>
+      </c>
+      <c r="AQ9">
+        <v>3.393617021276596</v>
       </c>
     </row>
     <row r="10">
@@ -1591,7 +1555,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Allianz Saudi Fransi Cooperative Insurance Company (SASE:8040)</t>
+          <t>Gulf Union Alahlia Cooperative Insurance Company (SASE:8120)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1600,28 +1564,28 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0519</v>
+        <v>0.193</v>
       </c>
       <c r="E10">
-        <v>-0.105</v>
+        <v>1.315</v>
       </c>
       <c r="G10">
-        <v>-0.06643783371472159</v>
+        <v>0.02217043941411452</v>
       </c>
       <c r="H10">
-        <v>-0.06643783371472159</v>
+        <v>0.02217043941411452</v>
       </c>
       <c r="I10">
-        <v>-0.008924485125858124</v>
+        <v>0.1657789613848202</v>
       </c>
       <c r="J10">
-        <v>-0.005174605679616332</v>
+        <v>0.1629827529538674</v>
       </c>
       <c r="K10">
-        <v>4.54</v>
+        <v>31.1</v>
       </c>
       <c r="L10">
-        <v>0.03463005339435546</v>
+        <v>0.2070572569906791</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1645,67 +1609,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>54.5</v>
+        <v>14.7</v>
       </c>
       <c r="V10">
-        <v>0.2605162523900574</v>
+        <v>0.07331670822942643</v>
       </c>
       <c r="W10">
-        <v>0.02399577167019028</v>
+        <v>0.3578826237054085</v>
       </c>
       <c r="X10">
-        <v>0.08270791729771995</v>
+        <v>0.07410688711067934</v>
       </c>
       <c r="Y10">
-        <v>-0.05871214562752967</v>
+        <v>0.2837757365947292</v>
       </c>
       <c r="Z10">
-        <v>0.9045371750289783</v>
+        <v>3.241260250323694</v>
       </c>
       <c r="AA10">
-        <v>-0.004680623203329064</v>
+        <v>0.5282695186376971</v>
       </c>
       <c r="AB10">
-        <v>0.08242154407149202</v>
+        <v>0.07386285120306117</v>
       </c>
       <c r="AC10">
-        <v>-0.08710216727482109</v>
+        <v>0.4544066674346359</v>
       </c>
       <c r="AD10">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AG10">
-        <v>-52.91</v>
+        <v>-12.89</v>
       </c>
       <c r="AH10">
-        <v>0.007543052326960483</v>
+        <v>0.00894666600761208</v>
       </c>
       <c r="AI10">
-        <v>0.008679513073857744</v>
+        <v>0.01327855623211797</v>
       </c>
       <c r="AJ10">
-        <v>-0.3385373344423828</v>
+        <v>-0.06870635893609081</v>
       </c>
       <c r="AK10">
-        <v>-0.4111430569585826</v>
+        <v>-0.1059945728147356</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AN10">
-        <v>-11.27659574468085</v>
+        <v>0.06418439716312058</v>
+      </c>
+      <c r="AO10">
+        <v>126.3959390862944</v>
       </c>
       <c r="AP10">
-        <v>375.2482269503546</v>
+        <v>-0.4570921985815602</v>
+      </c>
+      <c r="AQ10">
+        <v>126.3959390862944</v>
       </c>
     </row>
     <row r="11">
@@ -1716,7 +1686,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Saudi Arabian Cooperative Insurance Company (SASE:8100)</t>
+          <t>The Company for Cooperative Insurance (SASE:8010)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1725,73 +1695,76 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0167</v>
+        <v>0.125</v>
       </c>
       <c r="G11">
-        <v>-0.0799543118218161</v>
+        <v>0.03522919066627375</v>
       </c>
       <c r="H11">
-        <v>-0.0799543118218161</v>
+        <v>0.03522919066627375</v>
       </c>
       <c r="I11">
-        <v>-0.0930896630496859</v>
+        <v>0.07337851957028424</v>
       </c>
       <c r="J11">
-        <v>-0.0930896630496859</v>
+        <v>0.06550516362428135</v>
       </c>
       <c r="K11">
-        <v>-18.8</v>
+        <v>226.3</v>
       </c>
       <c r="L11">
-        <v>-0.1073672187321531</v>
+        <v>0.06062635625686501</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>33.4</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.00623134328358209</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>0.1475916924436589</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>33.4</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.00623134328358209</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>0.1475916924436589</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>2.45</v>
+        <v>690.9</v>
       </c>
       <c r="V11">
-        <v>0.02573529411764706</v>
+        <v>0.1288992537313433</v>
       </c>
       <c r="W11">
-        <v>-0.2243436754176611</v>
+        <v>0.2632619823173569</v>
       </c>
       <c r="X11">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y11">
-        <v>-0.3067862326161627</v>
+        <v>0.1894082513287301</v>
       </c>
       <c r="Z11">
-        <v>2.354760623991393</v>
+        <v>7.653680541316382</v>
       </c>
       <c r="AA11">
-        <v>-0.2192038730500269</v>
+        <v>0.5013555961869078</v>
       </c>
       <c r="AB11">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC11">
-        <v>-0.3016464302485284</v>
+        <v>0.427501865198281</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -1803,7 +1776,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>-2.45</v>
+        <v>-690.9</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1812,22 +1785,28 @@
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-0.02641509433962264</v>
+        <v>-0.147972842732004</v>
       </c>
       <c r="AK11">
-        <v>-0.03942075623491553</v>
+        <v>-2.692517537022603</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="AN11">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>9.712765957446807</v>
       </c>
       <c r="AP11">
-        <v>0.1560509554140128</v>
+        <v>-2.425061425061425</v>
+      </c>
+      <c r="AQ11">
+        <v>9.712765957446807</v>
       </c>
     </row>
     <row r="12">
@@ -1847,25 +1826,28 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.102</v>
+        <v>0.146</v>
+      </c>
+      <c r="E12">
+        <v>0.0312</v>
       </c>
       <c r="G12">
-        <v>-0.07812073204042611</v>
+        <v>-0.03690287525469776</v>
       </c>
       <c r="H12">
-        <v>-0.07812073204042611</v>
+        <v>-0.03690287525469776</v>
       </c>
       <c r="I12">
-        <v>-0.08003277792952745</v>
+        <v>0.056146705908988</v>
       </c>
       <c r="J12">
-        <v>-0.08003277792952745</v>
+        <v>0.05087933452989737</v>
       </c>
       <c r="K12">
-        <v>-31</v>
+        <v>35.2</v>
       </c>
       <c r="L12">
-        <v>-0.08467631794591642</v>
+        <v>0.07969209870953137</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1874,7 +1856,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1883,61 +1865,61 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>147.2</v>
+        <v>159.8</v>
       </c>
       <c r="V12">
-        <v>0.4497402994194928</v>
+        <v>0.3657587548638133</v>
       </c>
       <c r="W12">
-        <v>-0.1339092872570194</v>
+        <v>0.1757363954068897</v>
       </c>
       <c r="X12">
-        <v>0.08262283442835908</v>
+        <v>0.07390187069701128</v>
       </c>
       <c r="Y12">
-        <v>-0.2165321216853785</v>
+        <v>0.1018345247098784</v>
       </c>
       <c r="Z12">
-        <v>3.508721487444892</v>
+        <v>9.146821288051353</v>
       </c>
       <c r="AA12">
-        <v>-0.2808127276212383</v>
+        <v>0.4653841801999515</v>
       </c>
       <c r="AB12">
-        <v>0.08242824693692233</v>
+        <v>0.07384750991832814</v>
       </c>
       <c r="AC12">
-        <v>-0.3632409745581606</v>
+        <v>0.3915366702816234</v>
       </c>
       <c r="AD12">
-        <v>1.69</v>
+        <v>0.75</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.69</v>
+        <v>0.75</v>
       </c>
       <c r="AG12">
-        <v>-145.51</v>
+        <v>-159.05</v>
       </c>
       <c r="AH12">
-        <v>0.005136934253320769</v>
+        <v>0.001713698160630641</v>
       </c>
       <c r="AI12">
-        <v>0.008366750829248972</v>
+        <v>0.002301672548718736</v>
       </c>
       <c r="AJ12">
-        <v>-0.8004290665053082</v>
+        <v>-0.5724311678963471</v>
       </c>
       <c r="AK12">
-        <v>-2.655776601569628</v>
+        <v>-0.9578440228846733</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1946,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="AN12">
-        <v>-0.0597173144876325</v>
+        <v>0.02862595419847328</v>
       </c>
       <c r="AP12">
-        <v>5.141696113074205</v>
+        <v>-6.070610687022901</v>
       </c>
     </row>
     <row r="13">
@@ -1960,7 +1942,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wataniya Insurance Company (SASE:8300)</t>
+          <t>Saudi Arabian Cooperative Insurance Company (SASE:8100)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1969,25 +1951,28 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0892</v>
+        <v>0.05599999999999999</v>
+      </c>
+      <c r="E13">
+        <v>1.412</v>
       </c>
       <c r="G13">
-        <v>-0.08223684210526316</v>
+        <v>-0.03301544050862852</v>
       </c>
       <c r="H13">
-        <v>-0.08223684210526316</v>
+        <v>-0.03301544050862852</v>
       </c>
       <c r="I13">
-        <v>-0.04618421052631579</v>
+        <v>0.07720254314259764</v>
       </c>
       <c r="J13">
-        <v>-0.04618421052631579</v>
+        <v>0.07122895270034235</v>
       </c>
       <c r="K13">
-        <v>-8.220000000000001</v>
+        <v>20.4</v>
       </c>
       <c r="L13">
-        <v>-0.05407894736842106</v>
+        <v>0.09264305177111716</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -1996,7 +1981,7 @@
         <v>-0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P13">
         <v>-0</v>
@@ -2005,37 +1990,37 @@
         <v>-0</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
       <c r="U13">
-        <v>16.1</v>
+        <v>86.7</v>
       </c>
       <c r="V13">
-        <v>0.1117279666897988</v>
+        <v>0.7118226600985222</v>
       </c>
       <c r="W13">
-        <v>-0.1462633451957295</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="X13">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y13">
-        <v>-0.2287059023942311</v>
+        <v>0.2419357426955837</v>
       </c>
       <c r="Z13">
-        <v>6.468085106382978</v>
+        <v>3.543041029766694</v>
       </c>
       <c r="AA13">
-        <v>-0.2987234042553191</v>
+        <v>0.2523671019246241</v>
       </c>
       <c r="AB13">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC13">
-        <v>-0.3811659614538206</v>
+        <v>0.1785133709359973</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2047,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-16.1</v>
+        <v>-86.7</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -2056,10 +2041,10 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-0.12578125</v>
+        <v>-2.470085470085471</v>
       </c>
       <c r="AK13">
-        <v>-0.1963414634146342</v>
+        <v>10.44578313253012</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2068,10 +2053,10 @@
         <v>0</v>
       </c>
       <c r="AN13">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>2.761578044596913</v>
+        <v>-4.816666666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2082,7 +2067,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Gulf General Cooperative Insurance Company (SASE:8260)</t>
+          <t>Wataniya Insurance Company (SASE:8300)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2091,25 +2076,28 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.123</v>
+        <v>0.144</v>
+      </c>
+      <c r="E14">
+        <v>0.0704</v>
       </c>
       <c r="G14">
-        <v>-0.3017591339648173</v>
+        <v>-0.009009412819363514</v>
       </c>
       <c r="H14">
-        <v>-0.3017591339648173</v>
+        <v>-0.009009412819363514</v>
       </c>
       <c r="I14">
-        <v>-0.2760487144790257</v>
+        <v>0.07799193186911699</v>
       </c>
       <c r="J14">
-        <v>-0.2760487144790257</v>
+        <v>0.06367755900777296</v>
       </c>
       <c r="K14">
-        <v>-21.7</v>
+        <v>13.4</v>
       </c>
       <c r="L14">
-        <v>-0.2936400541271989</v>
+        <v>0.0600627521290901</v>
       </c>
       <c r="M14">
         <v>-0</v>
@@ -2118,7 +2106,7 @@
         <v>-0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P14">
         <v>-0</v>
@@ -2127,73 +2115,79 @@
         <v>-0</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>4.08</v>
+        <v>11.9</v>
       </c>
       <c r="V14">
-        <v>0.04503311258278146</v>
+        <v>0.06031424227065382</v>
       </c>
       <c r="W14">
-        <v>-0.2035647279549719</v>
+        <v>0.1365953109072375</v>
       </c>
       <c r="X14">
-        <v>0.08251153748758348</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y14">
-        <v>-0.2860762654425553</v>
+        <v>0.06274157991861073</v>
       </c>
       <c r="Z14">
-        <v>4.247614668352686</v>
+        <v>2.720731707317073</v>
       </c>
       <c r="AA14">
-        <v>-1.172548568801012</v>
+        <v>0.1732495538370018</v>
       </c>
       <c r="AB14">
-        <v>0.08244921059976001</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC14">
-        <v>-1.254997779400772</v>
+        <v>0.09939582284837498</v>
       </c>
       <c r="AD14">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>-3.901</v>
+        <v>-11.9</v>
       </c>
       <c r="AH14">
-        <v>0.001971821676819529</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>0.002113865303085771</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>-0.04499475195792339</v>
+        <v>-0.06418554476806904</v>
       </c>
       <c r="AK14">
-        <v>-0.04840010421965533</v>
+        <v>-0.1091743119266055</v>
       </c>
       <c r="AL14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AM14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AN14">
-        <v>-0.00873170731707317</v>
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>17.22772277227723</v>
       </c>
       <c r="AP14">
-        <v>0.1902926829268293</v>
+        <v>-0.6263157894736843</v>
+      </c>
+      <c r="AQ14">
+        <v>17.22772277227723</v>
       </c>
     </row>
     <row r="15">
@@ -2204,7 +2198,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Salama Cooperative Insurance Company (SASE:8050)</t>
+          <t>Arabian Shield Cooperative Insurance Company (SASE:8070)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2213,25 +2207,28 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.0561</v>
+        <v>0.164</v>
+      </c>
+      <c r="E15">
+        <v>0.0999</v>
       </c>
       <c r="G15">
-        <v>-0.2120743034055728</v>
+        <v>0.05884861407249467</v>
       </c>
       <c r="H15">
-        <v>-0.2120743034055728</v>
+        <v>0.05884861407249467</v>
       </c>
       <c r="I15">
-        <v>-0.2662538699690403</v>
+        <v>0.1565031982942431</v>
       </c>
       <c r="J15">
-        <v>-0.2662538699690403</v>
+        <v>0.1221630337098451</v>
       </c>
       <c r="K15">
-        <v>-36</v>
+        <v>18.9</v>
       </c>
       <c r="L15">
-        <v>-0.2786377708978328</v>
+        <v>0.08059701492537313</v>
       </c>
       <c r="M15">
         <v>-0</v>
@@ -2240,7 +2237,7 @@
         <v>-0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P15">
         <v>-0</v>
@@ -2249,73 +2246,79 @@
         <v>-0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>51.8</v>
+        <v>65.8</v>
       </c>
       <c r="V15">
-        <v>1.501449275362319</v>
+        <v>0.2063989962358846</v>
       </c>
       <c r="W15">
-        <v>-0.8035714285714286</v>
+        <v>0.06430758761483497</v>
       </c>
       <c r="X15">
-        <v>0.08711800332620187</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y15">
-        <v>-0.8906894318976305</v>
+        <v>-0.009546143373791824</v>
       </c>
       <c r="Z15">
-        <v>7.250280583613916</v>
+        <v>1.356275303643725</v>
       </c>
       <c r="AA15">
-        <v>-1.930415263748597</v>
+        <v>0.1656867056388588</v>
       </c>
       <c r="AB15">
-        <v>0.08284104883308525</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="AC15">
-        <v>-2.013256312581682</v>
+        <v>0.09183297465023196</v>
       </c>
       <c r="AD15">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>-47.18</v>
+        <v>-65.8</v>
       </c>
       <c r="AH15">
-        <v>0.1180981595092025</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>0.347107438016529</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>3.720820189274448</v>
+        <v>-0.2600790513833992</v>
       </c>
       <c r="AK15">
-        <v>1.225772928033255</v>
+        <v>-0.2517214996174446</v>
       </c>
       <c r="AL15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AM15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AN15">
-        <v>-0.1346938775510204</v>
+        <v>0</v>
+      </c>
+      <c r="AO15">
+        <v>2.936</v>
       </c>
       <c r="AP15">
-        <v>1.375510204081633</v>
+        <v>-1.691516709511568</v>
+      </c>
+      <c r="AQ15">
+        <v>2.936</v>
       </c>
     </row>
     <row r="16">
@@ -2326,7 +2329,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Mediterranean and Gulf Cooperative Insurance and Reinsurance Company (SASE:8030)</t>
+          <t>Aljazira Takaful Taawuni Company (SASE:8012)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2335,25 +2338,28 @@
         </is>
       </c>
       <c r="D16">
-        <v>-0.0491</v>
+        <v>0.442</v>
+      </c>
+      <c r="E16">
+        <v>0.07870000000000001</v>
       </c>
       <c r="G16">
-        <v>-0.06441374159820762</v>
+        <v>0.1294444444444444</v>
       </c>
       <c r="H16">
-        <v>-0.06441374159820762</v>
+        <v>0.1294444444444444</v>
       </c>
       <c r="I16">
-        <v>-0.1508588498879761</v>
+        <v>0.1680555555555555</v>
       </c>
       <c r="J16">
-        <v>-0.1508588498879761</v>
+        <v>0.15725</v>
       </c>
       <c r="K16">
-        <v>-77.59999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="L16">
-        <v>-0.1448842419716206</v>
+        <v>0.1569444444444444</v>
       </c>
       <c r="M16">
         <v>-0</v>
@@ -2362,7 +2368,7 @@
         <v>-0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P16">
         <v>-0</v>
@@ -2371,61 +2377,61 @@
         <v>-0</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
       <c r="U16">
-        <v>122.7</v>
+        <v>32.4</v>
       </c>
       <c r="V16">
-        <v>0.5093399750933998</v>
+        <v>0.1067897165458141</v>
       </c>
       <c r="W16">
-        <v>-0.3903420523138832</v>
+        <v>0.05062724014336918</v>
       </c>
       <c r="X16">
-        <v>0.0825976341140761</v>
+        <v>0.07389153448493359</v>
       </c>
       <c r="Y16">
-        <v>-0.4729396864279594</v>
+        <v>-0.02326429434156441</v>
       </c>
       <c r="Z16">
-        <v>92.66435986159168</v>
+        <v>0.5479702269510023</v>
       </c>
       <c r="AA16">
-        <v>-13.97923875432526</v>
+        <v>0.0861683181880451</v>
       </c>
       <c r="AB16">
-        <v>0.08243023847185627</v>
+        <v>0.07384884386358342</v>
       </c>
       <c r="AC16">
-        <v>-14.06166899279711</v>
+        <v>0.01231947432446168</v>
       </c>
       <c r="AD16">
-        <v>1.07</v>
+        <v>0.409</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.07</v>
+        <v>0.409</v>
       </c>
       <c r="AG16">
-        <v>-121.63</v>
+        <v>-31.991</v>
       </c>
       <c r="AH16">
-        <v>0.00442203578956069</v>
+        <v>0.00134624056561853</v>
       </c>
       <c r="AI16">
-        <v>0.004866512029835813</v>
+        <v>0.001639219426954539</v>
       </c>
       <c r="AJ16">
-        <v>-1.019787037813365</v>
+        <v>-0.1178700780003611</v>
       </c>
       <c r="AK16">
-        <v>-1.251723783060616</v>
+        <v>-0.1473499486433082</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2434,10 +2440,10 @@
         <v>0</v>
       </c>
       <c r="AN16">
-        <v>-0.01364795918367347</v>
+        <v>0.03122137404580153</v>
       </c>
       <c r="AP16">
-        <v>1.55140306122449</v>
+        <v>-2.44206106870229</v>
       </c>
     </row>
     <row r="17">
@@ -2448,7 +2454,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amana Cooperative Insurance Company (SASE:8310)</t>
+          <t>Chubb Arabia Cooperative Insurance Company (SASE:8240)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2457,25 +2463,28 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.186</v>
+        <v>0.0279</v>
+      </c>
+      <c r="E17">
+        <v>-0.162</v>
       </c>
       <c r="G17">
-        <v>-0.4922600619195047</v>
+        <v>0.08121951219512195</v>
       </c>
       <c r="H17">
-        <v>-0.4922600619195047</v>
+        <v>0.08121951219512195</v>
       </c>
       <c r="I17">
-        <v>-0.2894736842105263</v>
+        <v>0.141219512195122</v>
       </c>
       <c r="J17">
-        <v>-0.2894736842105263</v>
+        <v>0.07694795467639716</v>
       </c>
       <c r="K17">
-        <v>-19</v>
+        <v>3.46</v>
       </c>
       <c r="L17">
-        <v>-0.2941176470588235</v>
+        <v>0.08439024390243903</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2484,7 +2493,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2493,28 +2502,37 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>67.5</v>
+        <v>9.33</v>
       </c>
       <c r="V17">
-        <v>0.645933014354067</v>
+        <v>0.04240909090909091</v>
       </c>
       <c r="W17">
-        <v>-8.296943231441048</v>
+        <v>0.03619246861924686</v>
       </c>
       <c r="X17">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
       </c>
       <c r="Y17">
-        <v>-8.379385788639549</v>
+        <v>-0.03766126236937994</v>
+      </c>
+      <c r="Z17">
+        <v>1.012345679012346</v>
+      </c>
+      <c r="AA17">
+        <v>0.07789792942548848</v>
       </c>
       <c r="AB17">
-        <v>0.08244255719850152</v>
+        <v>0.0738537309886268</v>
+      </c>
+      <c r="AC17">
+        <v>0.004044198436861685</v>
       </c>
       <c r="AD17">
         <v>0</v>
@@ -2526,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>-67.5</v>
+        <v>-9.33</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2535,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="AJ17">
-        <v>-1.824324324324324</v>
+        <v>-0.044287273935539</v>
       </c>
       <c r="AK17">
-        <v>10.07462686567164</v>
+        <v>-0.09314165917939503</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -2547,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="AN17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>3.708791208791209</v>
+        <v>-1.555</v>
       </c>
     </row>
     <row r="18">
@@ -2561,7 +2579,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Allied Cooperative Insurance Group (SASE:8150)</t>
+          <t>Gulf Insurance Group (SASE:8250)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2570,100 +2588,121 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.059</v>
+        <v>0.0296</v>
+      </c>
+      <c r="E18">
+        <v>-0.09480000000000001</v>
       </c>
       <c r="G18">
-        <v>-0.1871988988300069</v>
+        <v>0.06605640771895102</v>
       </c>
       <c r="H18">
-        <v>-0.1871988988300069</v>
+        <v>0.06605640771895102</v>
       </c>
       <c r="I18">
-        <v>-0.2023399862353751</v>
+        <v>0.03067788223651658</v>
       </c>
       <c r="J18">
-        <v>-0.2023399862353751</v>
+        <v>0.02017967188674759</v>
       </c>
       <c r="K18">
-        <v>-28.6</v>
+        <v>10.1</v>
       </c>
       <c r="L18">
-        <v>-0.1968341362697866</v>
+        <v>0.02498762988619495</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>6.67</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.017877244706513</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>0.6603960396039604</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>6.67</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.017877244706513</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>0.6603960396039604</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>108.9</v>
+        <v>109.3</v>
       </c>
       <c r="V18">
-        <v>1.302631578947369</v>
+        <v>0.2929509514875368</v>
       </c>
       <c r="W18">
-        <v>-0.9533333333333334</v>
+        <v>0.0415296052631579</v>
       </c>
       <c r="X18">
-        <v>0.08272863520501803</v>
+        <v>0.07444826331158588</v>
       </c>
       <c r="Y18">
-        <v>-1.036061968538351</v>
+        <v>-0.03291865804842799</v>
+      </c>
+      <c r="Z18">
+        <v>2.79587742961887</v>
+      </c>
+      <c r="AA18">
+        <v>0.05641988916527203</v>
       </c>
       <c r="AB18">
-        <v>0.08241991681153951</v>
+        <v>0.0737783657831564</v>
+      </c>
+      <c r="AC18">
+        <v>-0.01735847661788437</v>
       </c>
       <c r="AD18">
-        <v>0.6850000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0.6850000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="AG18">
-        <v>-108.215</v>
+        <v>-101.39</v>
       </c>
       <c r="AH18">
-        <v>0.008127187518538293</v>
+        <v>0.02076060995774389</v>
       </c>
       <c r="AI18">
-        <v>0.01635430344992241</v>
+        <v>0.02847269716712861</v>
       </c>
       <c r="AJ18">
-        <v>4.396303067235424</v>
+        <v>-0.3731552022376798</v>
       </c>
       <c r="AK18">
-        <v>1.614787734089383</v>
+        <v>-0.6016853599192926</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>0.191</v>
       </c>
       <c r="AN18">
-        <v>-0.02362068965517242</v>
+        <v>0.5417808219178083</v>
+      </c>
+      <c r="AO18">
+        <v>64.92146596858639</v>
       </c>
       <c r="AP18">
-        <v>3.731551724137931</v>
+        <v>-6.944520547945205</v>
+      </c>
+      <c r="AQ18">
+        <v>64.92146596858639</v>
       </c>
     </row>
     <row r="19">
@@ -2674,7 +2713,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Gulf Union Alahlia Cooperative Insurance Company (SASE:8120)</t>
+          <t>Allianz Saudi Fransi Cooperative Insurance Company (SASE:8040)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2683,34 +2722,37 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.154</v>
+        <v>0.0114</v>
+      </c>
+      <c r="E19">
+        <v>0.0463</v>
       </c>
       <c r="G19">
-        <v>-0.2678018575851394</v>
+        <v>0.008754758020663405</v>
       </c>
       <c r="H19">
-        <v>-0.2678018575851394</v>
+        <v>0.008754758020663405</v>
       </c>
       <c r="I19">
-        <v>-0.06702786377708979</v>
+        <v>0.04230560087003806</v>
       </c>
       <c r="J19">
-        <v>-0.06702786377708979</v>
+        <v>0.03488053622754159</v>
       </c>
       <c r="K19">
-        <v>-9.210000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="L19">
-        <v>-0.07128482972136224</v>
+        <v>0.06579662860250135</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>0.778</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.002800575953923686</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>0.06429752066115703</v>
       </c>
       <c r="P19">
         <v>-0</v>
@@ -2719,70 +2761,204 @@
         <v>-0</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>0.778</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
       </c>
       <c r="U19">
-        <v>24.4</v>
+        <v>59.5</v>
       </c>
       <c r="V19">
-        <v>0.2343900096061479</v>
+        <v>0.2141828653707703</v>
       </c>
       <c r="W19">
-        <v>-0.233756345177665</v>
+        <v>0.06662995594713657</v>
       </c>
       <c r="X19">
-        <v>0.08305967385744673</v>
+        <v>0.07393852619101829</v>
       </c>
       <c r="Y19">
-        <v>-0.3168160190351117</v>
+        <v>-0.007308570243881721</v>
+      </c>
+      <c r="Z19">
+        <v>1.429015463516979</v>
+      </c>
+      <c r="AA19">
+        <v>0.04984482564492112</v>
       </c>
       <c r="AB19">
-        <v>0.08239417323749658</v>
+        <v>0.07384278722755101</v>
+      </c>
+      <c r="AC19">
+        <v>-0.02399796158262989</v>
       </c>
       <c r="AD19">
-        <v>1.84</v>
+        <v>0.84</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.84</v>
+        <v>0.84</v>
       </c>
       <c r="AG19">
-        <v>-22.56</v>
+        <v>-58.66</v>
       </c>
       <c r="AH19">
-        <v>0.0173683216915235</v>
+        <v>0.003014642549526271</v>
       </c>
       <c r="AI19">
-        <v>0.02073473067387874</v>
+        <v>0.004096761607491221</v>
       </c>
       <c r="AJ19">
-        <v>-0.2766740250183959</v>
+        <v>-0.2676827598795291</v>
       </c>
       <c r="AK19">
-        <v>-0.3506372396642835</v>
+        <v>-0.4030507077092209</v>
       </c>
       <c r="AL19">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>-0.2893081761006289</v>
-      </c>
-      <c r="AO19">
-        <v>-56.23376623376623</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="AP19">
-        <v>3.547169811320754</v>
-      </c>
-      <c r="AQ19">
-        <v>-56.23376623376623</v>
+        <v>-6.65079365079365</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Gulf General Cooperative Insurance Company (SASE:8260)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>0.179</v>
+      </c>
+      <c r="G20">
+        <v>-0.3266331658291458</v>
+      </c>
+      <c r="H20">
+        <v>-0.3266331658291458</v>
+      </c>
+      <c r="I20">
+        <v>-0.1253768844221106</v>
+      </c>
+      <c r="J20">
+        <v>-0.1253768844221106</v>
+      </c>
+      <c r="K20">
+        <v>-12.8</v>
+      </c>
+      <c r="L20">
+        <v>-0.1608040201005025</v>
+      </c>
+      <c r="M20">
+        <v>-0</v>
+      </c>
+      <c r="N20">
+        <v>-0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>-0</v>
+      </c>
+      <c r="Q20">
+        <v>-0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>1.42</v>
+      </c>
+      <c r="V20">
+        <v>0.01335841956726246</v>
+      </c>
+      <c r="W20">
+        <v>-0.1514792899408284</v>
+      </c>
+      <c r="X20">
+        <v>0.07402547118711106</v>
+      </c>
+      <c r="Y20">
+        <v>-0.2255047611279395</v>
+      </c>
+      <c r="Z20">
+        <v>1.121932655851386</v>
+      </c>
+      <c r="AA20">
+        <v>-0.1406644209220708</v>
+      </c>
+      <c r="AB20">
+        <v>0.07383163431417523</v>
+      </c>
+      <c r="AC20">
+        <v>-0.214496055236246</v>
+      </c>
+      <c r="AD20">
+        <v>0.651</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0.651</v>
+      </c>
+      <c r="AG20">
+        <v>-0.7689999999999999</v>
+      </c>
+      <c r="AH20">
+        <v>0.006086899608231808</v>
+      </c>
+      <c r="AI20">
+        <v>0.008224785536506173</v>
+      </c>
+      <c r="AJ20">
+        <v>-0.007286958334517819</v>
+      </c>
+      <c r="AK20">
+        <v>-0.00989309284584014</v>
+      </c>
+      <c r="AL20">
+        <v>1.89</v>
+      </c>
+      <c r="AM20">
+        <v>1.89</v>
+      </c>
+      <c r="AN20">
+        <v>-0.06955128205128205</v>
+      </c>
+      <c r="AO20">
+        <v>-5.280423280423281</v>
+      </c>
+      <c r="AP20">
+        <v>0.08215811965811966</v>
+      </c>
+      <c r="AQ20">
+        <v>-5.280423280423281</v>
       </c>
     </row>
   </sheetData>
